--- a/src/DashBoard/statistics_RCE.xlsx
+++ b/src/DashBoard/statistics_RCE.xlsx
@@ -411,16 +411,16 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>11854730</v>
+        <v>52702652</v>
       </c>
       <c r="C2">
-        <v>54844554.1</v>
+        <v>74550855.59999999</v>
       </c>
       <c r="D2">
-        <v>140544085</v>
+        <v>153769878</v>
       </c>
       <c r="E2">
-        <v>40917524.28545275</v>
+        <v>28171357.92633094</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -428,16 +428,16 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>11453611</v>
+        <v>24088207</v>
       </c>
       <c r="C3">
-        <v>24859557.7</v>
+        <v>60964954.8</v>
       </c>
       <c r="D3">
-        <v>71009355</v>
+        <v>101823923</v>
       </c>
       <c r="E3">
-        <v>17343416.8950569</v>
+        <v>18432925.05531118</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -445,16 +445,16 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>8775736</v>
+        <v>8373988</v>
       </c>
       <c r="C4">
-        <v>12179573</v>
+        <v>53390687.5</v>
       </c>
       <c r="D4">
-        <v>20995791</v>
+        <v>120182362</v>
       </c>
       <c r="E4">
-        <v>3277588.744952789</v>
+        <v>27728411.58385752</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -462,16 +462,16 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>8775736</v>
+        <v>8373988</v>
       </c>
       <c r="C5">
-        <v>10775593.1</v>
+        <v>35108229.7</v>
       </c>
       <c r="D5">
-        <v>11453611</v>
+        <v>60340122</v>
       </c>
       <c r="E5">
-        <v>1085078.074614306</v>
+        <v>18649742.45515801</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -479,16 +479,16 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>7335107</v>
+        <v>8373988</v>
       </c>
       <c r="C6">
-        <v>9562759.699999999</v>
+        <v>19520861.8</v>
       </c>
       <c r="D6">
-        <v>11493606</v>
+        <v>45780702</v>
       </c>
       <c r="E6">
-        <v>1638799.001447099</v>
+        <v>13608024.33807983</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -496,16 +496,16 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>6812286</v>
+        <v>8276488</v>
       </c>
       <c r="C7">
-        <v>8133199.6</v>
+        <v>11686635.7</v>
       </c>
       <c r="D7">
-        <v>10522367</v>
+        <v>40727527</v>
       </c>
       <c r="E7">
-        <v>1124425.924450446</v>
+        <v>9681961.151477989</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -513,16 +513,16 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>5227755</v>
+        <v>8276488</v>
       </c>
       <c r="C8">
-        <v>6812137.4</v>
+        <v>8387159.9</v>
       </c>
       <c r="D8">
-        <v>8257515</v>
+        <v>8798207</v>
       </c>
       <c r="E8">
-        <v>895674.3908284082</v>
+        <v>143786.4807500691</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -530,16 +530,16 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>4695734</v>
+        <v>6882859</v>
       </c>
       <c r="C9">
-        <v>5967057.3</v>
+        <v>8038640.9</v>
       </c>
       <c r="D9">
-        <v>7337407</v>
+        <v>8700707</v>
       </c>
       <c r="E9">
-        <v>1008482.94793517</v>
+        <v>616370.4045525627</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -547,16 +547,16 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>3954911</v>
+        <v>6882859</v>
       </c>
       <c r="C10">
-        <v>4817358.9</v>
+        <v>7856856.1</v>
       </c>
       <c r="D10">
-        <v>5248950</v>
+        <v>8373988</v>
       </c>
       <c r="E10">
-        <v>488462.5987220414</v>
+        <v>660769.8465101824</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -564,16 +564,16 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>3954911</v>
+        <v>6282427</v>
       </c>
       <c r="C11">
-        <v>4356954.4</v>
+        <v>7407482.2</v>
       </c>
       <c r="D11">
-        <v>5225455</v>
+        <v>8373988</v>
       </c>
       <c r="E11">
-        <v>520231.6883749394</v>
+        <v>898248.8127794882</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -581,16 +581,16 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>3954911</v>
+        <v>5792395</v>
       </c>
       <c r="C12">
-        <v>3955091.7</v>
+        <v>6637175.8</v>
       </c>
       <c r="D12">
-        <v>3956718</v>
+        <v>7984971</v>
       </c>
       <c r="E12">
-        <v>542.1</v>
+        <v>751807.4055603336</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -598,16 +598,16 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>3091460</v>
+        <v>5645382</v>
       </c>
       <c r="C13">
-        <v>3725298.7</v>
+        <v>5762992.4</v>
       </c>
       <c r="D13">
-        <v>3954911</v>
+        <v>5792395</v>
       </c>
       <c r="E13">
-        <v>358871.8047618258</v>
+        <v>58805.2</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -615,16 +615,16 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>3091460</v>
+        <v>5645382</v>
       </c>
       <c r="C14">
-        <v>3467882.9</v>
+        <v>5714248.4</v>
       </c>
       <c r="D14">
-        <v>3971106</v>
+        <v>5792395</v>
       </c>
       <c r="E14">
-        <v>409884.0409158302</v>
+        <v>70105.81483044042</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -632,16 +632,16 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>2896527</v>
+        <v>5645382</v>
       </c>
       <c r="C15">
-        <v>3054092.9</v>
+        <v>5645382</v>
       </c>
       <c r="D15">
-        <v>3107655</v>
+        <v>5645382</v>
       </c>
       <c r="E15">
-        <v>78928.46468727237</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -649,16 +649,16 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>2308106</v>
+        <v>2656407</v>
       </c>
       <c r="C16">
-        <v>2798336.1</v>
+        <v>5019263</v>
       </c>
       <c r="D16">
-        <v>3093960</v>
+        <v>5645382</v>
       </c>
       <c r="E16">
-        <v>252001.9955363251</v>
+        <v>1182700.533881675</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -666,16 +666,16 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>1983189</v>
+        <v>1955875</v>
       </c>
       <c r="C17">
-        <v>2418668.9</v>
+        <v>3982464.1</v>
       </c>
       <c r="D17">
-        <v>2896527</v>
+        <v>5645382</v>
       </c>
       <c r="E17">
-        <v>334928.3079909639</v>
+        <v>1625238.182094209</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -683,16 +683,16 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>1858887</v>
+        <v>1955875</v>
       </c>
       <c r="C18">
-        <v>2026971</v>
+        <v>2586823.4</v>
       </c>
       <c r="D18">
-        <v>2327315</v>
+        <v>5503762</v>
       </c>
       <c r="E18">
-        <v>157660.2547625748</v>
+        <v>1004221.719807852</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -700,16 +700,16 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>1533970</v>
+        <v>1491756</v>
       </c>
       <c r="C19">
-        <v>1848981</v>
+        <v>1998604.7</v>
       </c>
       <c r="D19">
-        <v>2308106</v>
+        <v>2565396</v>
       </c>
       <c r="E19">
-        <v>238574.6338775353</v>
+        <v>281807.4419198507</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -717,16 +717,16 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>1530363</v>
+        <v>1147839</v>
       </c>
       <c r="C20">
-        <v>1680761.3</v>
+        <v>1598307.2</v>
       </c>
       <c r="D20">
-        <v>1983189</v>
+        <v>1955875</v>
       </c>
       <c r="E20">
-        <v>181969.436454065</v>
+        <v>302907.7070025786</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -734,16 +734,16 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>1530363</v>
+        <v>1147839</v>
       </c>
       <c r="C21">
-        <v>57071398.4</v>
+        <v>89803501.59999999</v>
       </c>
       <c r="D21">
-        <v>163692692</v>
+        <v>203603803</v>
       </c>
       <c r="E21">
-        <v>55892755.09221047</v>
+        <v>59724089.03715536</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -751,16 +751,16 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>953590</v>
+        <v>1147839</v>
       </c>
       <c r="C22">
-        <v>14128518.3</v>
+        <v>27299221.3</v>
       </c>
       <c r="D22">
-        <v>62330778</v>
+        <v>105930250</v>
       </c>
       <c r="E22">
-        <v>19325621.28771375</v>
+        <v>32876563.22208722</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -768,16 +768,16 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>949587</v>
+        <v>901324</v>
       </c>
       <c r="C23">
-        <v>1233819.7</v>
+        <v>4393341.4</v>
       </c>
       <c r="D23">
-        <v>1983189</v>
+        <v>34259706</v>
       </c>
       <c r="E23">
-        <v>364936.736033809</v>
+        <v>9955959.280406134</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -785,16 +785,16 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>384758</v>
+        <v>901324</v>
       </c>
       <c r="C24">
-        <v>897979.5</v>
+        <v>991818.9</v>
       </c>
       <c r="D24">
-        <v>1547158</v>
+        <v>1147839</v>
       </c>
       <c r="E24">
-        <v>311221.0555210717</v>
+        <v>106815.2180276294</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -802,16 +802,16 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>380755</v>
+        <v>888624</v>
       </c>
       <c r="C25">
-        <v>611188.7</v>
+        <v>957627.2</v>
       </c>
       <c r="D25">
-        <v>962584</v>
+        <v>1147839</v>
       </c>
       <c r="E25">
-        <v>279795.6007488503</v>
+        <v>98407.16333255421</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -819,16 +819,16 @@
         <v>24</v>
       </c>
       <c r="B26">
-        <v>380755</v>
+        <v>888624</v>
       </c>
       <c r="C26">
-        <v>381955.9</v>
+        <v>898784</v>
       </c>
       <c r="D26">
-        <v>384758</v>
+        <v>901324</v>
       </c>
       <c r="E26">
-        <v>1834.405050690823</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -836,16 +836,16 @@
         <v>25</v>
       </c>
       <c r="B27">
-        <v>380655</v>
+        <v>632900</v>
       </c>
       <c r="C27">
-        <v>380765</v>
+        <v>842559.2</v>
       </c>
       <c r="D27">
-        <v>381055</v>
+        <v>901324</v>
       </c>
       <c r="E27">
-        <v>104.4030650891055</v>
+        <v>104983.3464705712</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -853,16 +853,16 @@
         <v>26</v>
       </c>
       <c r="B28">
-        <v>117531</v>
+        <v>625800</v>
       </c>
       <c r="C28">
-        <v>330370.2</v>
+        <v>762442</v>
       </c>
       <c r="D28">
-        <v>397551</v>
+        <v>901324</v>
       </c>
       <c r="E28">
-        <v>106535.42381931</v>
+        <v>133896.8976638369</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -870,16 +870,16 @@
         <v>27</v>
       </c>
       <c r="B29">
-        <v>117531</v>
+        <v>577891</v>
       </c>
       <c r="C29">
-        <v>196948.4</v>
+        <v>643810.5</v>
       </c>
       <c r="D29">
-        <v>381254</v>
+        <v>887523</v>
       </c>
       <c r="E29">
-        <v>120444.3269159656</v>
+        <v>83634.03146357348</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -887,16 +887,16 @@
         <v>28</v>
       </c>
       <c r="B30">
-        <v>114331</v>
+        <v>514682</v>
       </c>
       <c r="C30">
-        <v>117181.3</v>
+        <v>594704.6</v>
       </c>
       <c r="D30">
-        <v>120434</v>
+        <v>632900</v>
       </c>
       <c r="E30">
-        <v>1663.866223588904</v>
+        <v>45218.65013288212</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -904,16 +904,16 @@
         <v>29</v>
       </c>
       <c r="B31">
-        <v>114331</v>
+        <v>514682</v>
       </c>
       <c r="C31">
-        <v>116251</v>
+        <v>550367.4</v>
       </c>
       <c r="D31">
-        <v>117531</v>
+        <v>625800</v>
       </c>
       <c r="E31">
-        <v>1567.673435381234</v>
+        <v>38401.93369662522</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -921,16 +921,16 @@
         <v>30</v>
       </c>
       <c r="B32">
-        <v>114331</v>
+        <v>476275</v>
       </c>
       <c r="C32">
-        <v>115601.1</v>
+        <v>507000.6</v>
       </c>
       <c r="D32">
-        <v>122536</v>
+        <v>514682</v>
       </c>
       <c r="E32">
-        <v>2519.096959229636</v>
+        <v>15362.8</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -938,16 +938,16 @@
         <v>31</v>
       </c>
       <c r="B33">
-        <v>22315</v>
+        <v>445268</v>
       </c>
       <c r="C33">
-        <v>105159.4</v>
+        <v>477755</v>
       </c>
       <c r="D33">
-        <v>114631</v>
+        <v>514682</v>
       </c>
       <c r="E33">
-        <v>27614.94484948322</v>
+        <v>20731.77511936689</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -955,16 +955,16 @@
         <v>32</v>
       </c>
       <c r="B34">
-        <v>22315</v>
+        <v>432663</v>
       </c>
       <c r="C34">
-        <v>105279.3</v>
+        <v>455149.8</v>
       </c>
       <c r="D34">
-        <v>115530</v>
+        <v>476275</v>
       </c>
       <c r="E34">
-        <v>27657.07708363268</v>
+        <v>17852.19463707474</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -972,16 +972,16 @@
         <v>33</v>
       </c>
       <c r="B35">
-        <v>9010</v>
+        <v>432663</v>
       </c>
       <c r="C35">
-        <v>75183.89999999999</v>
+        <v>438424.7</v>
       </c>
       <c r="D35">
-        <v>117534</v>
+        <v>465070</v>
       </c>
       <c r="E35">
-        <v>48789.56796170673</v>
+        <v>10178.47645819353</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -989,16 +989,16 @@
         <v>34</v>
       </c>
       <c r="B36">
-        <v>9010</v>
+        <v>430860</v>
       </c>
       <c r="C36">
-        <v>54470</v>
+        <v>432482.7</v>
       </c>
       <c r="D36">
-        <v>117534</v>
+        <v>432663</v>
       </c>
       <c r="E36">
-        <v>49760.68725208686</v>
+        <v>540.9</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1006,16 +1006,16 @@
         <v>35</v>
       </c>
       <c r="B37">
-        <v>8910</v>
+        <v>428160</v>
       </c>
       <c r="C37">
-        <v>25523.3</v>
+        <v>490894.8</v>
       </c>
       <c r="D37">
-        <v>115130</v>
+        <v>1021292</v>
       </c>
       <c r="E37">
-        <v>32754.28981996098</v>
+        <v>176822.0779172103</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1023,16 +1023,16 @@
         <v>36</v>
       </c>
       <c r="B38">
-        <v>5806</v>
+        <v>258647</v>
       </c>
       <c r="C38">
-        <v>8898.200000000001</v>
+        <v>396238</v>
       </c>
       <c r="D38">
-        <v>12210</v>
+        <v>432663</v>
       </c>
       <c r="E38">
-        <v>1825.148585732132</v>
+        <v>68810.52791252223</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1040,16 +1040,16 @@
         <v>37</v>
       </c>
       <c r="B39">
-        <v>5806</v>
+        <v>258647</v>
       </c>
       <c r="C39">
-        <v>8717.9</v>
+        <v>342673</v>
       </c>
       <c r="D39">
-        <v>22215</v>
+        <v>430860</v>
       </c>
       <c r="E39">
-        <v>4741.907832297038</v>
+        <v>83578.49064203062</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1057,16 +1057,16 @@
         <v>38</v>
       </c>
       <c r="B40">
-        <v>5806</v>
+        <v>148136</v>
       </c>
       <c r="C40">
-        <v>8377.700000000001</v>
+        <v>256996.3</v>
       </c>
       <c r="D40">
-        <v>21011</v>
+        <v>415455</v>
       </c>
       <c r="E40">
-        <v>4458.926531128316</v>
+        <v>70977.56663207045</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1074,16 +1074,16 @@
         <v>39</v>
       </c>
       <c r="B41">
-        <v>5806</v>
+        <v>148136</v>
       </c>
       <c r="C41">
-        <v>58938588.1</v>
+        <v>94600134.7</v>
       </c>
       <c r="D41">
-        <v>153578955</v>
+        <v>201683381</v>
       </c>
       <c r="E41">
-        <v>46587914.7435165</v>
+        <v>63626319.5626779</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1091,16 +1091,16 @@
         <v>40</v>
       </c>
       <c r="B42">
-        <v>1003</v>
+        <v>130128</v>
       </c>
       <c r="C42">
-        <v>24356859.1</v>
+        <v>43721208</v>
       </c>
       <c r="D42">
-        <v>54899055</v>
+        <v>87462227</v>
       </c>
       <c r="E42">
-        <v>20342940.17888649</v>
+        <v>31884449.59778455</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1108,16 +1108,16 @@
         <v>41</v>
       </c>
       <c r="B43">
-        <v>1003</v>
+        <v>130127</v>
       </c>
       <c r="C43">
-        <v>7005471.1</v>
+        <v>8640379.1</v>
       </c>
       <c r="D43">
-        <v>52906490</v>
+        <v>34622755</v>
       </c>
       <c r="E43">
-        <v>15668399.86597447</v>
+        <v>12719814.04485087</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1125,16 +1125,16 @@
         <v>42</v>
       </c>
       <c r="B44">
-        <v>1003</v>
+        <v>130127</v>
       </c>
       <c r="C44">
-        <v>3734.2</v>
+        <v>1395088.4</v>
       </c>
       <c r="D44">
-        <v>24012</v>
+        <v>10530816</v>
       </c>
       <c r="E44">
-        <v>6862.405930867103</v>
+        <v>3108176.594726664</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1142,16 +1142,16 @@
         <v>43</v>
       </c>
       <c r="B45">
-        <v>602</v>
+        <v>130127</v>
       </c>
       <c r="C45">
-        <v>1142.7</v>
+        <v>340459.5</v>
       </c>
       <c r="D45">
-        <v>3003</v>
+        <v>2160648</v>
       </c>
       <c r="E45">
-        <v>645.4488438288506</v>
+        <v>607117.6089920717</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1159,16 +1159,16 @@
         <v>44</v>
       </c>
       <c r="B46">
-        <v>602</v>
+        <v>123126</v>
       </c>
       <c r="C46">
-        <v>972.6</v>
+        <v>136117.1</v>
       </c>
       <c r="D46">
-        <v>1401</v>
+        <v>202928</v>
       </c>
       <c r="E46">
-        <v>326.1239641608694</v>
+        <v>22450.86373594566</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1176,16 +1176,16 @@
         <v>45</v>
       </c>
       <c r="B47">
-        <v>602</v>
+        <v>123126</v>
       </c>
       <c r="C47">
-        <v>682.2</v>
+        <v>126036.5</v>
       </c>
       <c r="D47">
-        <v>1003</v>
+        <v>130127</v>
       </c>
       <c r="E47">
-        <v>160.4</v>
+        <v>3354.967995376409</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1193,16 +1193,16 @@
         <v>46</v>
       </c>
       <c r="B48">
-        <v>502</v>
+        <v>59318</v>
       </c>
       <c r="C48">
-        <v>622.1</v>
+        <v>110465</v>
       </c>
       <c r="D48">
-        <v>1003</v>
+        <v>130127</v>
       </c>
       <c r="E48">
-        <v>132.951457306793</v>
+        <v>25730.02436065695</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1210,16 +1210,16 @@
         <v>47</v>
       </c>
       <c r="B49">
-        <v>101</v>
+        <v>58717</v>
       </c>
       <c r="C49">
-        <v>1002.2</v>
+        <v>96363.60000000001</v>
       </c>
       <c r="D49">
-        <v>5305</v>
+        <v>123126</v>
       </c>
       <c r="E49">
-        <v>1455.658325294779</v>
+        <v>30555.03689148485</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1227,16 +1227,16 @@
         <v>48</v>
       </c>
       <c r="B50">
-        <v>101</v>
+        <v>57917</v>
       </c>
       <c r="C50">
-        <v>231.6</v>
+        <v>105093.2</v>
       </c>
       <c r="D50">
-        <v>603</v>
+        <v>397451</v>
       </c>
       <c r="E50">
-        <v>174.0822793968415</v>
+        <v>100479.5460736164</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -1244,16 +1244,16 @@
         <v>49</v>
       </c>
       <c r="B51">
-        <v>101</v>
+        <v>57917</v>
       </c>
       <c r="C51">
-        <v>251.1</v>
+        <v>65768.5</v>
       </c>
       <c r="D51">
-        <v>900</v>
+        <v>129827</v>
       </c>
       <c r="E51">
-        <v>249.8605411024318</v>
+        <v>21361.45871072479</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1261,16 +1261,16 @@
         <v>50</v>
       </c>
       <c r="B52">
-        <v>101</v>
+        <v>57817</v>
       </c>
       <c r="C52">
-        <v>151.2</v>
+        <v>58187.3</v>
       </c>
       <c r="D52">
-        <v>603</v>
+        <v>59318</v>
       </c>
       <c r="E52">
-        <v>150.6</v>
+        <v>571.4352194256144</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1278,16 +1278,16 @@
         <v>51</v>
       </c>
       <c r="B53">
-        <v>101</v>
+        <v>57817</v>
       </c>
       <c r="C53">
-        <v>161.2</v>
+        <v>57827.1</v>
       </c>
       <c r="D53">
-        <v>502</v>
+        <v>57917</v>
       </c>
       <c r="E53">
-        <v>128.4373777371681</v>
+        <v>29.96814975936953</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1295,16 +1295,16 @@
         <v>52</v>
       </c>
       <c r="B54">
-        <v>101</v>
+        <v>57817</v>
       </c>
       <c r="C54">
-        <v>141.1</v>
+        <v>57817</v>
       </c>
       <c r="D54">
-        <v>502</v>
+        <v>57817</v>
       </c>
       <c r="E54">
-        <v>120.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -1312,16 +1312,16 @@
         <v>53</v>
       </c>
       <c r="B55">
-        <v>101</v>
+        <v>57817</v>
       </c>
       <c r="C55">
-        <v>241.2</v>
+        <v>57817.1</v>
       </c>
       <c r="D55">
-        <v>1102</v>
+        <v>57818</v>
       </c>
       <c r="E55">
-        <v>310.8442696914325</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -1329,16 +1329,16 @@
         <v>54</v>
       </c>
       <c r="B56">
-        <v>101</v>
+        <v>57817</v>
       </c>
       <c r="C56">
-        <v>251.2</v>
+        <v>64308.2</v>
       </c>
       <c r="D56">
-        <v>1102</v>
+        <v>122727</v>
       </c>
       <c r="E56">
-        <v>307.7664049242542</v>
+        <v>19472.93333732748</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -1346,16 +1346,16 @@
         <v>55</v>
       </c>
       <c r="B57">
-        <v>101</v>
+        <v>57817</v>
       </c>
       <c r="C57">
-        <v>201.1</v>
+        <v>64307.9</v>
       </c>
       <c r="D57">
-        <v>501</v>
+        <v>122726</v>
       </c>
       <c r="E57">
-        <v>154.9196243217753</v>
+        <v>19472.7</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1363,16 +1363,16 @@
         <v>56</v>
       </c>
       <c r="B58">
-        <v>101</v>
+        <v>56621</v>
       </c>
       <c r="C58">
-        <v>261</v>
+        <v>57577.8</v>
       </c>
       <c r="D58">
-        <v>1701</v>
+        <v>57817</v>
       </c>
       <c r="E58">
-        <v>480</v>
+        <v>478.4</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1380,16 +1380,16 @@
         <v>57</v>
       </c>
       <c r="B59">
-        <v>101</v>
+        <v>8206</v>
       </c>
       <c r="C59">
-        <v>241.2</v>
+        <v>43535</v>
       </c>
       <c r="D59">
-        <v>1001</v>
+        <v>62618</v>
       </c>
       <c r="E59">
-        <v>280.0788460416102</v>
+        <v>22417.3850125299</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1397,16 +1397,16 @@
         <v>58</v>
       </c>
       <c r="B60">
-        <v>101</v>
+        <v>8206</v>
       </c>
       <c r="C60">
-        <v>1032.3</v>
+        <v>28663.1</v>
       </c>
       <c r="D60">
-        <v>3505</v>
+        <v>56721</v>
       </c>
       <c r="E60">
-        <v>1365.951686554103</v>
+        <v>22890.93922253956</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -1414,16 +1414,16 @@
         <v>59</v>
       </c>
       <c r="B61">
-        <v>101</v>
+        <v>8206</v>
       </c>
       <c r="C61">
-        <v>68426773.7</v>
+        <v>78845607.5</v>
       </c>
       <c r="D61">
-        <v>190564285</v>
+        <v>201691673</v>
       </c>
       <c r="E61">
-        <v>48719059.94053191</v>
+        <v>51974736.89276519</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -1431,16 +1431,16 @@
         <v>60</v>
       </c>
       <c r="B62">
-        <v>101</v>
+        <v>202</v>
       </c>
       <c r="C62">
-        <v>31117558.2</v>
+        <v>48371357.7</v>
       </c>
       <c r="D62">
-        <v>109918872</v>
+        <v>201691673</v>
       </c>
       <c r="E62">
-        <v>31798463.86987531</v>
+        <v>58325156.79491403</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -1448,16 +1448,16 @@
         <v>61</v>
       </c>
       <c r="B63">
-        <v>101</v>
+        <v>202</v>
       </c>
       <c r="C63">
-        <v>8693091.800000001</v>
+        <v>9375568.199999999</v>
       </c>
       <c r="D63">
-        <v>33077929</v>
+        <v>44403491</v>
       </c>
       <c r="E63">
-        <v>9404681.67382101</v>
+        <v>16496266.59184181</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -1465,16 +1465,16 @@
         <v>62</v>
       </c>
       <c r="B64">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C64">
-        <v>2744758.1</v>
+        <v>482.4</v>
       </c>
       <c r="D64">
-        <v>7305506</v>
+        <v>1703</v>
       </c>
       <c r="E64">
-        <v>2825457.200403024</v>
+        <v>611.5032624606348</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -1482,16 +1482,16 @@
         <v>63</v>
       </c>
       <c r="B65">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C65">
-        <v>181.2</v>
+        <v>132.8</v>
       </c>
       <c r="D65">
-        <v>502</v>
+        <v>202</v>
       </c>
       <c r="E65">
-        <v>125.2523852068295</v>
+        <v>45.3029800344304</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -1499,16 +1499,16 @@
         <v>64</v>
       </c>
       <c r="B66">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C66">
-        <v>291</v>
+        <v>113.1</v>
       </c>
       <c r="D66">
-        <v>1102</v>
+        <v>203</v>
       </c>
       <c r="E66">
-        <v>359.0824417873979</v>
+        <v>29.96814975936953</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -1516,16 +1516,16 @@
         <v>65</v>
       </c>
       <c r="B67">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C67">
-        <v>271</v>
+        <v>113</v>
       </c>
       <c r="D67">
-        <v>1002</v>
+        <v>203</v>
       </c>
       <c r="E67">
-        <v>340.7641413059772</v>
+        <v>30</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -1533,16 +1533,16 @@
         <v>66</v>
       </c>
       <c r="B68">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C68">
-        <v>270.9</v>
+        <v>102.9</v>
       </c>
       <c r="D68">
-        <v>900</v>
+        <v>103</v>
       </c>
       <c r="E68">
-        <v>315.9656468668707</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -1550,16 +1550,16 @@
         <v>67</v>
       </c>
       <c r="B69">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C69">
-        <v>401.1</v>
+        <v>122.7</v>
       </c>
       <c r="D69">
-        <v>1403</v>
+        <v>303</v>
       </c>
       <c r="E69">
-        <v>473.6037267589857</v>
+        <v>60.10166387047866</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -1567,16 +1567,16 @@
         <v>68</v>
       </c>
       <c r="B70">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C70">
-        <v>401.2</v>
+        <v>852.7</v>
       </c>
       <c r="D70">
-        <v>1102</v>
+        <v>7306</v>
       </c>
       <c r="E70">
-        <v>392.6326018047916</v>
+        <v>2152.024955710319</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -1584,16 +1584,16 @@
         <v>69</v>
       </c>
       <c r="B71">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C71">
-        <v>401.4</v>
+        <v>132.5</v>
       </c>
       <c r="D71">
-        <v>1701</v>
+        <v>303</v>
       </c>
       <c r="E71">
-        <v>466.9477915142119</v>
+        <v>64.26702109169211</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -1601,16 +1601,16 @@
         <v>70</v>
       </c>
       <c r="B72">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C72">
-        <v>241.3</v>
+        <v>132.2</v>
       </c>
       <c r="D72">
-        <v>900</v>
+        <v>303</v>
       </c>
       <c r="E72">
-        <v>232.9729812660687</v>
+        <v>64.25075875038364</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -1618,16 +1618,16 @@
         <v>71</v>
       </c>
       <c r="B73">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C73">
-        <v>201.5</v>
+        <v>122.1</v>
       </c>
       <c r="D73">
-        <v>603</v>
+        <v>303</v>
       </c>
       <c r="E73">
-        <v>148.9310243031988</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -1635,16 +1635,16 @@
         <v>72</v>
       </c>
       <c r="B74">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C74">
-        <v>351.4</v>
+        <v>102</v>
       </c>
       <c r="D74">
-        <v>2504</v>
+        <v>102</v>
       </c>
       <c r="E74">
-        <v>718.1649114235532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -1652,16 +1652,16 @@
         <v>73</v>
       </c>
       <c r="B75">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C75">
-        <v>121.1</v>
+        <v>132.2</v>
       </c>
       <c r="D75">
-        <v>202</v>
+        <v>303</v>
       </c>
       <c r="E75">
-        <v>40.20062188573704</v>
+        <v>64.25075875038364</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -1669,16 +1669,16 @@
         <v>74</v>
       </c>
       <c r="B76">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C76">
-        <v>281.3</v>
+        <v>132.2</v>
       </c>
       <c r="D76">
-        <v>1101</v>
+        <v>303</v>
       </c>
       <c r="E76">
-        <v>299.3863891361797</v>
+        <v>64.40621088062858</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -1686,16 +1686,16 @@
         <v>75</v>
       </c>
       <c r="B77">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C77">
-        <v>141.3</v>
+        <v>842.5</v>
       </c>
       <c r="D77">
-        <v>202</v>
+        <v>7306</v>
       </c>
       <c r="E77">
-        <v>49.35797807852343</v>
+        <v>2155.333257294565</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -1703,16 +1703,16 @@
         <v>76</v>
       </c>
       <c r="B78">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C78">
-        <v>381.3</v>
+        <v>102</v>
       </c>
       <c r="D78">
-        <v>2904</v>
+        <v>102</v>
       </c>
       <c r="E78">
-        <v>840.8999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -1720,16 +1720,16 @@
         <v>77</v>
       </c>
       <c r="B79">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C79">
-        <v>151</v>
+        <v>112.1</v>
       </c>
       <c r="D79">
-        <v>501</v>
+        <v>202</v>
       </c>
       <c r="E79">
-        <v>120.415945787923</v>
+        <v>29.96814975936953</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -1737,16 +1737,16 @@
         <v>78</v>
       </c>
       <c r="B80">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C80">
-        <v>221.2</v>
+        <v>102</v>
       </c>
       <c r="D80">
-        <v>1102</v>
+        <v>102</v>
       </c>
       <c r="E80">
-        <v>299.6533997804797</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -1754,16 +1754,16 @@
         <v>79</v>
       </c>
       <c r="B81">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C81">
-        <v>82412209.09999999</v>
+        <v>55639348.2</v>
       </c>
       <c r="D81">
-        <v>153810754</v>
+        <v>132001901</v>
       </c>
       <c r="E81">
-        <v>53786663.2774647</v>
+        <v>47424888.49978751</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -1771,16 +1771,16 @@
         <v>80</v>
       </c>
       <c r="B82">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C82">
-        <v>33931458.5</v>
+        <v>13438285.3</v>
       </c>
       <c r="D82">
-        <v>137536525</v>
+        <v>64871879</v>
       </c>
       <c r="E82">
-        <v>47640915.03543633</v>
+        <v>21489387.59105955</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -1791,13 +1791,13 @@
         <v>101</v>
       </c>
       <c r="C83">
-        <v>11266653.3</v>
+        <v>738663.4</v>
       </c>
       <c r="D83">
-        <v>53027826</v>
+        <v>5365240</v>
       </c>
       <c r="E83">
-        <v>17635004.2451669</v>
+        <v>1590099.008859838</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -1808,13 +1808,13 @@
         <v>101</v>
       </c>
       <c r="C84">
-        <v>3741.5</v>
+        <v>3802</v>
       </c>
       <c r="D84">
-        <v>32501</v>
+        <v>10302</v>
       </c>
       <c r="E84">
-        <v>9620.321244636272</v>
+        <v>3353.711496238161</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -1825,13 +1825,13 @@
         <v>101</v>
       </c>
       <c r="C85">
-        <v>401.5</v>
+        <v>611.4</v>
       </c>
       <c r="D85">
-        <v>1701</v>
+        <v>5102</v>
       </c>
       <c r="E85">
-        <v>469.1273281317131</v>
+        <v>1497.16146089859</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -1842,13 +1842,13 @@
         <v>101</v>
       </c>
       <c r="C86">
-        <v>411.2</v>
+        <v>201.1</v>
       </c>
       <c r="D86">
-        <v>1102</v>
+        <v>901</v>
       </c>
       <c r="E86">
-        <v>393.5433394176555</v>
+        <v>240.8735975568929</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -1856,16 +1856,16 @@
         <v>85</v>
       </c>
       <c r="B87">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C87">
-        <v>171.4</v>
+        <v>90.8</v>
       </c>
       <c r="D87">
-        <v>302</v>
+        <v>201</v>
       </c>
       <c r="E87">
-        <v>90.46678948652925</v>
+        <v>54.18634514340307</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -1873,16 +1873,16 @@
         <v>86</v>
       </c>
       <c r="B88">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C88">
-        <v>180.9</v>
+        <v>150.5</v>
       </c>
       <c r="D88">
-        <v>900</v>
+        <v>1102</v>
       </c>
       <c r="E88">
-        <v>239.7</v>
+        <v>320.7030558008452</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -1890,16 +1890,16 @@
         <v>87</v>
       </c>
       <c r="B89">
+        <v>0</v>
+      </c>
+      <c r="C89">
+        <v>30.2</v>
+      </c>
+      <c r="D89">
         <v>101</v>
       </c>
-      <c r="C89">
-        <v>311.6</v>
-      </c>
-      <c r="D89">
-        <v>1102</v>
-      </c>
       <c r="E89">
-        <v>305.3009007520286</v>
+        <v>46.13198456602534</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -1907,16 +1907,16 @@
         <v>88</v>
       </c>
       <c r="B90">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C90">
-        <v>201.4</v>
+        <v>1380.9</v>
       </c>
       <c r="D90">
-        <v>503</v>
+        <v>6804</v>
       </c>
       <c r="E90">
-        <v>155.5006109312758</v>
+        <v>2712.201778998015</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -1924,16 +1924,16 @@
         <v>89</v>
       </c>
       <c r="B91">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C91">
-        <v>141.1</v>
+        <v>240.4</v>
       </c>
       <c r="D91">
-        <v>502</v>
+        <v>1202</v>
       </c>
       <c r="E91">
-        <v>120.3</v>
+        <v>436.9535902129653</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -1941,16 +1941,16 @@
         <v>90</v>
       </c>
       <c r="B92">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C92">
-        <v>261.3</v>
+        <v>100.1</v>
       </c>
       <c r="D92">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E92">
-        <v>276.7746556316167</v>
+        <v>300.3</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -1958,16 +1958,16 @@
         <v>91</v>
       </c>
       <c r="B93">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C93">
-        <v>171.2</v>
+        <v>20.1</v>
       </c>
       <c r="D93">
-        <v>502</v>
+        <v>201</v>
       </c>
       <c r="E93">
-        <v>127.2484184577553</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -1975,16 +1975,16 @@
         <v>92</v>
       </c>
       <c r="B94">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C94">
-        <v>541.1</v>
+        <v>0</v>
       </c>
       <c r="D94">
-        <v>1701</v>
+        <v>0</v>
       </c>
       <c r="E94">
-        <v>569.6420718310753</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -1992,16 +1992,16 @@
         <v>93</v>
       </c>
       <c r="B95">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C95">
-        <v>811.5</v>
+        <v>0</v>
       </c>
       <c r="D95">
-        <v>2904</v>
+        <v>0</v>
       </c>
       <c r="E95">
-        <v>1026.026924597985</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2009,16 +2009,16 @@
         <v>94</v>
       </c>
       <c r="B96">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C96">
-        <v>171.3</v>
+        <v>30.2</v>
       </c>
       <c r="D96">
-        <v>502</v>
+        <v>201</v>
       </c>
       <c r="E96">
-        <v>119.0722889676687</v>
+        <v>64.40621088062859</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2026,16 +2026,16 @@
         <v>95</v>
       </c>
       <c r="B97">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C97">
-        <v>151</v>
+        <v>20.1</v>
       </c>
       <c r="D97">
-        <v>501</v>
+        <v>201</v>
       </c>
       <c r="E97">
-        <v>120.415945787923</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2043,16 +2043,16 @@
         <v>96</v>
       </c>
       <c r="B98">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C98">
-        <v>371.1</v>
+        <v>0</v>
       </c>
       <c r="D98">
-        <v>1102</v>
+        <v>0</v>
       </c>
       <c r="E98">
-        <v>415.0497440066673</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2060,16 +2060,16 @@
         <v>97</v>
       </c>
       <c r="B99">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C99">
-        <v>301.1</v>
+        <v>0</v>
       </c>
       <c r="D99">
-        <v>1102</v>
+        <v>0</v>
       </c>
       <c r="E99">
-        <v>357.827178956546</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2077,16 +2077,16 @@
         <v>98</v>
       </c>
       <c r="B100">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C100">
-        <v>251</v>
+        <v>10</v>
       </c>
       <c r="D100">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="E100">
-        <v>280.1074793717583</v>
+        <v>30</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2094,16 +2094,16 @@
         <v>99</v>
       </c>
       <c r="B101">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C101">
-        <v>58836927.9</v>
+        <v>55443271.3</v>
       </c>
       <c r="D101">
-        <v>155808902</v>
+        <v>108290521</v>
       </c>
       <c r="E101">
-        <v>49065341.11572044</v>
+        <v>37351022.84770288</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2111,16 +2111,16 @@
         <v>0</v>
       </c>
       <c r="B102">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C102">
-        <v>17625847.1</v>
+        <v>20809495.8</v>
       </c>
       <c r="D102">
-        <v>55210603</v>
+        <v>60890943</v>
       </c>
       <c r="E102">
-        <v>19993797.368708</v>
+        <v>17248472.82039243</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2128,16 +2128,16 @@
         <v>1</v>
       </c>
       <c r="B103">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C103">
-        <v>7710216.6</v>
+        <v>9039222</v>
       </c>
       <c r="D103">
-        <v>25721214</v>
+        <v>27365057</v>
       </c>
       <c r="E103">
-        <v>9081319.184522556</v>
+        <v>9064865.973173061</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2145,16 +2145,16 @@
         <v>2</v>
       </c>
       <c r="B104">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C104">
-        <v>619013</v>
+        <v>1664301.8</v>
       </c>
       <c r="D104">
-        <v>2778069</v>
+        <v>8320357</v>
       </c>
       <c r="E104">
-        <v>1073711.22388294</v>
+        <v>3328002.369046026</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2162,16 +2162,16 @@
         <v>3</v>
       </c>
       <c r="B105">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C105">
-        <v>67702.10000000001</v>
+        <v>40.2</v>
       </c>
       <c r="D105">
-        <v>225438</v>
+        <v>201</v>
       </c>
       <c r="E105">
-        <v>102869.984033682</v>
+        <v>66.66453329919891</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -2179,13 +2179,13 @@
         <v>4</v>
       </c>
       <c r="B106">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C106">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="D106">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -2196,16 +2196,16 @@
         <v>5</v>
       </c>
       <c r="B107">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C107">
-        <v>171.2</v>
+        <v>10</v>
       </c>
       <c r="D107">
-        <v>502</v>
+        <v>100</v>
       </c>
       <c r="E107">
-        <v>127.2484184577553</v>
+        <v>30</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -2213,13 +2213,13 @@
         <v>6</v>
       </c>
       <c r="B108">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C108">
-        <v>121.1</v>
+        <v>20.1</v>
       </c>
       <c r="D108">
-        <v>302</v>
+        <v>201</v>
       </c>
       <c r="E108">
         <v>60.3</v>
@@ -2230,16 +2230,16 @@
         <v>7</v>
       </c>
       <c r="B109">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C109">
-        <v>181.2</v>
+        <v>140.3</v>
       </c>
       <c r="D109">
-        <v>502</v>
+        <v>901</v>
       </c>
       <c r="E109">
-        <v>160.4</v>
+        <v>261.832408230914</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -2247,16 +2247,16 @@
         <v>8</v>
       </c>
       <c r="B110">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C110">
-        <v>111</v>
+        <v>100.3</v>
       </c>
       <c r="D110">
-        <v>201</v>
+        <v>501</v>
       </c>
       <c r="E110">
-        <v>30</v>
+        <v>161.6174804901995</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -2264,16 +2264,16 @@
         <v>9</v>
       </c>
       <c r="B111">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C111">
-        <v>2321.8</v>
+        <v>40.2</v>
       </c>
       <c r="D111">
-        <v>20611</v>
+        <v>201</v>
       </c>
       <c r="E111">
-        <v>6104.321220250456</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -2281,16 +2281,16 @@
         <v>10</v>
       </c>
       <c r="B112">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C112">
-        <v>401.1</v>
+        <v>90.3</v>
       </c>
       <c r="D112">
-        <v>1701</v>
+        <v>501</v>
       </c>
       <c r="E112">
-        <v>505.8658814349907</v>
+        <v>158.1967445935598</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -2298,16 +2298,16 @@
         <v>11</v>
       </c>
       <c r="B113">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C113">
-        <v>251.2</v>
+        <v>320.5</v>
       </c>
       <c r="D113">
-        <v>1101</v>
+        <v>1802</v>
       </c>
       <c r="E113">
-        <v>320.3753423720371</v>
+        <v>558.8026932648053</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -2315,16 +2315,16 @@
         <v>12</v>
       </c>
       <c r="B114">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C114">
-        <v>321.4</v>
+        <v>820.7</v>
       </c>
       <c r="D114">
-        <v>1002</v>
+        <v>6804</v>
       </c>
       <c r="E114">
-        <v>285.9794398204179</v>
+        <v>2015.478456843437</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -2332,16 +2332,16 @@
         <v>13</v>
       </c>
       <c r="B115">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C115">
-        <v>151.1</v>
+        <v>100.1</v>
       </c>
       <c r="D115">
-        <v>501</v>
+        <v>901</v>
       </c>
       <c r="E115">
-        <v>120.4578349465073</v>
+        <v>268.6263017651101</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -2349,16 +2349,16 @@
         <v>14</v>
       </c>
       <c r="B116">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C116">
-        <v>251.4</v>
+        <v>60.4</v>
       </c>
       <c r="D116">
-        <v>502</v>
+        <v>201</v>
       </c>
       <c r="E116">
-        <v>175.1006567663297</v>
+        <v>80.45023306367732</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -2366,16 +2366,16 @@
         <v>15</v>
       </c>
       <c r="B117">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C117">
-        <v>131.1</v>
+        <v>30.2</v>
       </c>
       <c r="D117">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E117">
-        <v>45.97923444338759</v>
+        <v>64.40621088062859</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -2383,16 +2383,16 @@
         <v>16</v>
       </c>
       <c r="B118">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C118">
-        <v>291.3</v>
+        <v>220.3</v>
       </c>
       <c r="D118">
-        <v>1102</v>
+        <v>1001</v>
       </c>
       <c r="E118">
-        <v>324.293401104617</v>
+        <v>371.3330176539652</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -2400,16 +2400,16 @@
         <v>17</v>
       </c>
       <c r="B119">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C119">
-        <v>281.2</v>
+        <v>40.2</v>
       </c>
       <c r="D119">
-        <v>900</v>
+        <v>402</v>
       </c>
       <c r="E119">
-        <v>271.2348797629095</v>
+        <v>120.6</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -2417,16 +2417,16 @@
         <v>18</v>
       </c>
       <c r="B120">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C120">
-        <v>181.2</v>
+        <v>250.5</v>
       </c>
       <c r="D120">
-        <v>502</v>
+        <v>1102</v>
       </c>
       <c r="E120">
-        <v>160.4</v>
+        <v>418.3905472163538</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -2434,16 +2434,16 @@
         <v>19</v>
       </c>
       <c r="B121">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C121">
-        <v>69961895.59999999</v>
+        <v>57107986.6</v>
       </c>
       <c r="D121">
-        <v>101754126</v>
+        <v>133569167</v>
       </c>
       <c r="E121">
-        <v>29183852.97897062</v>
+        <v>41109686.23328209</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -2451,16 +2451,16 @@
         <v>20</v>
       </c>
       <c r="B122">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C122">
-        <v>40570553.9</v>
+        <v>31334509.8</v>
       </c>
       <c r="D122">
-        <v>87214369</v>
+        <v>133628642</v>
       </c>
       <c r="E122">
-        <v>27404984.32903394</v>
+        <v>36932804.65184764</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -2468,16 +2468,16 @@
         <v>21</v>
       </c>
       <c r="B123">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C123">
-        <v>9509867.5</v>
+        <v>7855174.1</v>
       </c>
       <c r="D123">
-        <v>39468582</v>
+        <v>45548850</v>
       </c>
       <c r="E123">
-        <v>15318248.97264658</v>
+        <v>14062206.87106145</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -2485,16 +2485,16 @@
         <v>22</v>
       </c>
       <c r="B124">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C124">
-        <v>77675</v>
+        <v>2291.1</v>
       </c>
       <c r="D124">
-        <v>348562</v>
+        <v>22710</v>
       </c>
       <c r="E124">
-        <v>114290.7690253242</v>
+        <v>6806.563809294672</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -2502,16 +2502,16 @@
         <v>23</v>
       </c>
       <c r="B125">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C125">
-        <v>17534.4</v>
+        <v>2701.3</v>
       </c>
       <c r="D125">
-        <v>118126</v>
+        <v>24110</v>
       </c>
       <c r="E125">
-        <v>34595.57970377141</v>
+        <v>7160.028548127445</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -2519,16 +2519,16 @@
         <v>24</v>
       </c>
       <c r="B126">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C126">
-        <v>211.1</v>
+        <v>140.3</v>
       </c>
       <c r="D126">
-        <v>1102</v>
+        <v>1001</v>
       </c>
       <c r="E126">
-        <v>298.4595282446181</v>
+        <v>297.6511548776521</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -2536,16 +2536,16 @@
         <v>25</v>
       </c>
       <c r="B127">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C127">
-        <v>141.1</v>
+        <v>0</v>
       </c>
       <c r="D127">
-        <v>502</v>
+        <v>0</v>
       </c>
       <c r="E127">
-        <v>120.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -2553,16 +2553,16 @@
         <v>26</v>
       </c>
       <c r="B128">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C128">
-        <v>201.2</v>
+        <v>20.1</v>
       </c>
       <c r="D128">
-        <v>1002</v>
+        <v>201</v>
       </c>
       <c r="E128">
-        <v>268.6264320576067</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -2570,16 +2570,16 @@
         <v>27</v>
       </c>
       <c r="B129">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C129">
-        <v>601.5</v>
+        <v>40.2</v>
       </c>
       <c r="D129">
-        <v>3805</v>
+        <v>201</v>
       </c>
       <c r="E129">
-        <v>1107.475259317336</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -2587,16 +2587,16 @@
         <v>28</v>
       </c>
       <c r="B130">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C130">
-        <v>121.1</v>
+        <v>30.1</v>
       </c>
       <c r="D130">
-        <v>302</v>
+        <v>201</v>
       </c>
       <c r="E130">
-        <v>60.3</v>
+        <v>64.29688950485864</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -2604,16 +2604,16 @@
         <v>29</v>
       </c>
       <c r="B131">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C131">
-        <v>301.2</v>
+        <v>20.1</v>
       </c>
       <c r="D131">
-        <v>1702</v>
+        <v>201</v>
       </c>
       <c r="E131">
-        <v>475.7101638603069</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -2621,16 +2621,16 @@
         <v>30</v>
       </c>
       <c r="B132">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C132">
-        <v>200.9</v>
+        <v>0</v>
       </c>
       <c r="D132">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="E132">
-        <v>236.3473926236547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -2638,16 +2638,16 @@
         <v>31</v>
       </c>
       <c r="B133">
+        <v>0</v>
+      </c>
+      <c r="C133">
+        <v>20.1</v>
+      </c>
+      <c r="D133">
         <v>101</v>
       </c>
-      <c r="C133">
-        <v>281.2</v>
-      </c>
-      <c r="D133">
-        <v>1102</v>
-      </c>
       <c r="E133">
-        <v>319.1685448160579</v>
+        <v>40.20062188573704</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -2655,16 +2655,16 @@
         <v>32</v>
       </c>
       <c r="B134">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C134">
-        <v>151.1</v>
+        <v>20.1</v>
       </c>
       <c r="D134">
-        <v>502</v>
+        <v>201</v>
       </c>
       <c r="E134">
-        <v>120.7066278213421</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -2672,16 +2672,16 @@
         <v>33</v>
       </c>
       <c r="B135">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C135">
-        <v>281.2</v>
+        <v>680.7</v>
       </c>
       <c r="D135">
-        <v>1803</v>
+        <v>6404</v>
       </c>
       <c r="E135">
-        <v>508.142066749054</v>
+        <v>1908.892246827987</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -2689,16 +2689,16 @@
         <v>34</v>
       </c>
       <c r="B136">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C136">
-        <v>281</v>
+        <v>130.3</v>
       </c>
       <c r="D136">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E136">
-        <v>337.0759558319163</v>
+        <v>297.1232235958677</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -2706,16 +2706,16 @@
         <v>35</v>
       </c>
       <c r="B137">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C137">
-        <v>101</v>
+        <v>60.3</v>
       </c>
       <c r="D137">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="E137">
-        <v>0</v>
+        <v>92.10977146861238</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -2723,16 +2723,16 @@
         <v>36</v>
       </c>
       <c r="B138">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C138">
-        <v>981.5</v>
+        <v>110.1</v>
       </c>
       <c r="D138">
-        <v>8505</v>
+        <v>1101</v>
       </c>
       <c r="E138">
-        <v>2510.681471234454</v>
+        <v>330.3</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -2740,16 +2740,16 @@
         <v>37</v>
       </c>
       <c r="B139">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C139">
-        <v>201.1</v>
+        <v>50.3</v>
       </c>
       <c r="D139">
-        <v>1002</v>
+        <v>302</v>
       </c>
       <c r="E139">
-        <v>268.6263017651101</v>
+        <v>103.1038796554232</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -2757,16 +2757,16 @@
         <v>38</v>
       </c>
       <c r="B140">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C140">
-        <v>141.1</v>
+        <v>10</v>
       </c>
       <c r="D140">
-        <v>502</v>
+        <v>100</v>
       </c>
       <c r="E140">
-        <v>120.3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -2774,16 +2774,16 @@
         <v>39</v>
       </c>
       <c r="B141">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C141">
-        <v>90054411.09999999</v>
+        <v>72449406.09999999</v>
       </c>
       <c r="D141">
-        <v>229242738</v>
+        <v>169651914</v>
       </c>
       <c r="E141">
-        <v>61557685.80115813</v>
+        <v>61910794.71005272</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -2791,16 +2791,16 @@
         <v>40</v>
       </c>
       <c r="B142">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C142">
-        <v>38246340.4</v>
+        <v>20593370.4</v>
       </c>
       <c r="D142">
-        <v>106402755</v>
+        <v>121764408</v>
       </c>
       <c r="E142">
-        <v>44836581.79305128</v>
+        <v>36572037.09847622</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -2808,16 +2808,16 @@
         <v>41</v>
       </c>
       <c r="B143">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C143">
-        <v>144201.3</v>
+        <v>672665.7</v>
       </c>
       <c r="D143">
-        <v>1440301</v>
+        <v>6502926</v>
       </c>
       <c r="E143">
-        <v>432033.2460357767</v>
+        <v>1943744.571382879</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -2825,16 +2825,16 @@
         <v>42</v>
       </c>
       <c r="B144">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C144">
-        <v>251.3</v>
+        <v>9560.299999999999</v>
       </c>
       <c r="D144">
-        <v>1002</v>
+        <v>29001</v>
       </c>
       <c r="E144">
-        <v>280.5533995516718</v>
+        <v>11999.50349847859</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -2842,16 +2842,16 @@
         <v>43</v>
       </c>
       <c r="B145">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C145">
-        <v>451.1</v>
+        <v>100.1</v>
       </c>
       <c r="D145">
-        <v>2702</v>
+        <v>1001</v>
       </c>
       <c r="E145">
-        <v>786.6449580338007</v>
+        <v>300.3</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -2859,16 +2859,16 @@
         <v>44</v>
       </c>
       <c r="B146">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C146">
-        <v>221.1</v>
+        <v>20.1</v>
       </c>
       <c r="D146">
-        <v>900</v>
+        <v>201</v>
       </c>
       <c r="E146">
-        <v>235.5340527397259</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -2876,16 +2876,16 @@
         <v>45</v>
       </c>
       <c r="B147">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C147">
-        <v>441.5</v>
+        <v>40.2</v>
       </c>
       <c r="D147">
-        <v>2904</v>
+        <v>201</v>
       </c>
       <c r="E147">
-        <v>829.361712402978</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -2893,16 +2893,16 @@
         <v>46</v>
       </c>
       <c r="B148">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C148">
-        <v>131.1</v>
+        <v>50.2</v>
       </c>
       <c r="D148">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E148">
-        <v>45.97923444338759</v>
+        <v>80.99481464884033</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -2910,16 +2910,16 @@
         <v>47</v>
       </c>
       <c r="B149">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C149">
-        <v>380.9</v>
+        <v>220.3</v>
       </c>
       <c r="D149">
         <v>1701</v>
       </c>
       <c r="E149">
-        <v>507.4407256025081</v>
+        <v>499.8881975002011</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -2927,16 +2927,16 @@
         <v>48</v>
       </c>
       <c r="B150">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C150">
-        <v>261.1</v>
+        <v>110.1</v>
       </c>
       <c r="D150">
-        <v>900</v>
+        <v>1001</v>
       </c>
       <c r="E150">
-        <v>249.5762208224173</v>
+        <v>298.4595282446181</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -2944,16 +2944,16 @@
         <v>49</v>
       </c>
       <c r="B151">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C151">
-        <v>180.9</v>
+        <v>40.2</v>
       </c>
       <c r="D151">
-        <v>900</v>
+        <v>201</v>
       </c>
       <c r="E151">
-        <v>239.7</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -2961,16 +2961,16 @@
         <v>50</v>
       </c>
       <c r="B152">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C152">
-        <v>161.1</v>
+        <v>20.1</v>
       </c>
       <c r="D152">
-        <v>702</v>
+        <v>201</v>
       </c>
       <c r="E152">
-        <v>180.3</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -2978,16 +2978,16 @@
         <v>51</v>
       </c>
       <c r="B153">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C153">
-        <v>111</v>
+        <v>110.1</v>
       </c>
       <c r="D153">
-        <v>201</v>
+        <v>1001</v>
       </c>
       <c r="E153">
-        <v>30</v>
+        <v>298.4595282446181</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -2995,16 +2995,16 @@
         <v>52</v>
       </c>
       <c r="B154">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C154">
-        <v>401.4</v>
+        <v>30.2</v>
       </c>
       <c r="D154">
-        <v>2904</v>
+        <v>201</v>
       </c>
       <c r="E154">
-        <v>835.1412096166732</v>
+        <v>64.40621088062858</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -3012,16 +3012,16 @@
         <v>53</v>
       </c>
       <c r="B155">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C155">
-        <v>241.4</v>
+        <v>40.2</v>
       </c>
       <c r="D155">
-        <v>1102</v>
+        <v>201</v>
       </c>
       <c r="E155">
-        <v>294.2248120060577</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -3029,16 +3029,16 @@
         <v>54</v>
       </c>
       <c r="B156">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C156">
-        <v>190.9</v>
+        <v>40.2</v>
       </c>
       <c r="D156">
-        <v>900</v>
+        <v>201</v>
       </c>
       <c r="E156">
-        <v>238.2395643045042</v>
+        <v>66.66453329919891</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -3046,16 +3046,16 @@
         <v>55</v>
       </c>
       <c r="B157">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C157">
-        <v>101</v>
+        <v>110.3</v>
       </c>
       <c r="D157">
-        <v>101</v>
+        <v>1001</v>
       </c>
       <c r="E157">
-        <v>0</v>
+        <v>298.4533631909683</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -3063,16 +3063,16 @@
         <v>56</v>
       </c>
       <c r="B158">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C158">
-        <v>861.5</v>
+        <v>30.1</v>
       </c>
       <c r="D158">
-        <v>6905</v>
+        <v>201</v>
       </c>
       <c r="E158">
-        <v>2020.68341162093</v>
+        <v>64.29688950485863</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -3080,16 +3080,16 @@
         <v>57</v>
       </c>
       <c r="B159">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C159">
-        <v>821.3</v>
+        <v>140.3</v>
       </c>
       <c r="D159">
-        <v>6505</v>
+        <v>901</v>
       </c>
       <c r="E159">
-        <v>1909.484121431755</v>
+        <v>265.6618339167296</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -3097,16 +3097,16 @@
         <v>58</v>
       </c>
       <c r="B160">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C160">
-        <v>270.8</v>
+        <v>30.2</v>
       </c>
       <c r="D160">
-        <v>900</v>
+        <v>201</v>
       </c>
       <c r="E160">
-        <v>315.9875946932094</v>
+        <v>64.40621088062859</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -3114,16 +3114,16 @@
         <v>59</v>
       </c>
       <c r="B161">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C161">
-        <v>61520042.3</v>
+        <v>76278491.7</v>
       </c>
       <c r="D161">
-        <v>120769089</v>
+        <v>124821613</v>
       </c>
       <c r="E161">
-        <v>39181118.93455732</v>
+        <v>41440042.05244108</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -3131,16 +3131,16 @@
         <v>60</v>
       </c>
       <c r="B162">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C162">
-        <v>15778032.2</v>
+        <v>50081113.6</v>
       </c>
       <c r="D162">
-        <v>43668700</v>
+        <v>143318058</v>
       </c>
       <c r="E162">
-        <v>12684706.26343344</v>
+        <v>47573527.53650111</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -3148,16 +3148,16 @@
         <v>61</v>
       </c>
       <c r="B163">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C163">
-        <v>4486986</v>
+        <v>5151720.6</v>
       </c>
       <c r="D163">
-        <v>15968962</v>
+        <v>50726609</v>
       </c>
       <c r="E163">
-        <v>5832776.740782884</v>
+        <v>15192829.69807743</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -3165,16 +3165,16 @@
         <v>62</v>
       </c>
       <c r="B164">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C164">
-        <v>871.3</v>
+        <v>1060.8</v>
       </c>
       <c r="D164">
-        <v>2702</v>
+        <v>8605</v>
       </c>
       <c r="E164">
-        <v>834.5288551032852</v>
+        <v>2541.988623105934</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -3182,16 +3182,16 @@
         <v>63</v>
       </c>
       <c r="B165">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C165">
-        <v>580.9</v>
+        <v>220.3</v>
       </c>
       <c r="D165">
-        <v>1701</v>
+        <v>1001</v>
       </c>
       <c r="E165">
-        <v>534.3748590643089</v>
+        <v>392.2858779002884</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -3199,16 +3199,16 @@
         <v>64</v>
       </c>
       <c r="B166">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C166">
-        <v>461</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="D166">
-        <v>1701</v>
+        <v>201</v>
       </c>
       <c r="E166">
-        <v>523.8513147831167</v>
+        <v>98.46948765988377</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -3216,16 +3216,16 @@
         <v>65</v>
       </c>
       <c r="B167">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C167">
-        <v>121.1</v>
+        <v>2471.2</v>
       </c>
       <c r="D167">
-        <v>302</v>
+        <v>23409</v>
       </c>
       <c r="E167">
-        <v>60.3</v>
+        <v>6985.453382565801</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -3233,16 +3233,16 @@
         <v>66</v>
       </c>
       <c r="B168">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C168">
-        <v>221.4</v>
+        <v>330.5</v>
       </c>
       <c r="D168">
-        <v>502</v>
+        <v>1001</v>
       </c>
       <c r="E168">
-        <v>154.026750923338</v>
+        <v>424.7708205609232</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -3250,16 +3250,16 @@
         <v>67</v>
       </c>
       <c r="B169">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C169">
-        <v>201.2</v>
+        <v>60.2</v>
       </c>
       <c r="D169">
-        <v>703</v>
+        <v>301</v>
       </c>
       <c r="E169">
-        <v>205.427262066163</v>
+        <v>102.3531142662499</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -3267,16 +3267,16 @@
         <v>68</v>
       </c>
       <c r="B170">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C170">
-        <v>241.1</v>
+        <v>210.2</v>
       </c>
       <c r="D170">
-        <v>900</v>
+        <v>1001</v>
       </c>
       <c r="E170">
-        <v>253.6381083354786</v>
+        <v>396.5049306124704</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -3284,16 +3284,16 @@
         <v>69</v>
       </c>
       <c r="B171">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C171">
-        <v>571.6</v>
+        <v>0</v>
       </c>
       <c r="D171">
-        <v>2904</v>
+        <v>0</v>
       </c>
       <c r="E171">
-        <v>962.4746438218516</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -3301,16 +3301,16 @@
         <v>70</v>
       </c>
       <c r="B172">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C172">
-        <v>101</v>
+        <v>100.1</v>
       </c>
       <c r="D172">
-        <v>101</v>
+        <v>1001</v>
       </c>
       <c r="E172">
-        <v>0</v>
+        <v>300.3</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -3318,16 +3318,16 @@
         <v>71</v>
       </c>
       <c r="B173">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C173">
-        <v>311.3</v>
+        <v>10</v>
       </c>
       <c r="D173">
-        <v>1002</v>
+        <v>100</v>
       </c>
       <c r="E173">
-        <v>281.2369285851344</v>
+        <v>30</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -3335,16 +3335,16 @@
         <v>72</v>
       </c>
       <c r="B174">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C174">
-        <v>671.4</v>
+        <v>20</v>
       </c>
       <c r="D174">
-        <v>5304</v>
+        <v>100</v>
       </c>
       <c r="E174">
-        <v>1546.875832120988</v>
+        <v>40</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -3352,16 +3352,16 @@
         <v>73</v>
       </c>
       <c r="B175">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C175">
-        <v>2041.8</v>
+        <v>40.3</v>
       </c>
       <c r="D175">
-        <v>17809</v>
+        <v>201</v>
       </c>
       <c r="E175">
-        <v>5262.08344289598</v>
+        <v>66.75485001106661</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -3369,16 +3369,16 @@
         <v>74</v>
       </c>
       <c r="B176">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C176">
-        <v>151.3</v>
+        <v>40.2</v>
       </c>
       <c r="D176">
-        <v>402</v>
+        <v>301</v>
       </c>
       <c r="E176">
-        <v>92.57542870546158</v>
+        <v>92.00086956110795</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -3386,16 +3386,16 @@
         <v>75</v>
       </c>
       <c r="B177">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C177">
-        <v>131.2</v>
+        <v>100.1</v>
       </c>
       <c r="D177">
-        <v>302</v>
+        <v>1001</v>
       </c>
       <c r="E177">
-        <v>64.40621088062858</v>
+        <v>300.3</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -3403,16 +3403,16 @@
         <v>76</v>
       </c>
       <c r="B178">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C178">
-        <v>351.4</v>
+        <v>30.1</v>
       </c>
       <c r="D178">
-        <v>1102</v>
+        <v>201</v>
       </c>
       <c r="E178">
-        <v>380.6316329471317</v>
+        <v>64.29688950485864</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -3420,16 +3420,16 @@
         <v>77</v>
       </c>
       <c r="B179">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C179">
-        <v>191.1</v>
+        <v>30.2</v>
       </c>
       <c r="D179">
-        <v>1002</v>
+        <v>201</v>
       </c>
       <c r="E179">
-        <v>270.3</v>
+        <v>64.40621088062858</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -3437,16 +3437,16 @@
         <v>78</v>
       </c>
       <c r="B180">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C180">
-        <v>340.5</v>
+        <v>20.1</v>
       </c>
       <c r="D180">
-        <v>900</v>
+        <v>201</v>
       </c>
       <c r="E180">
-        <v>366.2789237725807</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -3454,16 +3454,16 @@
         <v>79</v>
       </c>
       <c r="B181">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C181">
-        <v>68727592.2</v>
+        <v>62814025.1</v>
       </c>
       <c r="D181">
-        <v>221354254</v>
+        <v>130541792</v>
       </c>
       <c r="E181">
-        <v>76834988.07368414</v>
+        <v>41888492.33681633</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -3471,16 +3471,16 @@
         <v>80</v>
       </c>
       <c r="B182">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C182">
-        <v>13190931.9</v>
+        <v>24413900.2</v>
       </c>
       <c r="D182">
-        <v>61459266</v>
+        <v>71937783</v>
       </c>
       <c r="E182">
-        <v>19346543.24702637</v>
+        <v>23160325.73392997</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -3488,16 +3488,16 @@
         <v>81</v>
       </c>
       <c r="B183">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C183">
-        <v>4243455</v>
+        <v>8955970.9</v>
       </c>
       <c r="D183">
-        <v>27826685</v>
+        <v>27487687</v>
       </c>
       <c r="E183">
-        <v>7993485.048507378</v>
+        <v>9604038.129360676</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -3505,16 +3505,16 @@
         <v>82</v>
       </c>
       <c r="B184">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C184">
-        <v>745490.3</v>
+        <v>22321.6</v>
       </c>
       <c r="D184">
-        <v>3653945</v>
+        <v>67600</v>
       </c>
       <c r="E184">
-        <v>1293433.732684829</v>
+        <v>28190.13381380088</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -3522,16 +3522,16 @@
         <v>83</v>
       </c>
       <c r="B185">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C185">
-        <v>95771.10000000001</v>
+        <v>220.4</v>
       </c>
       <c r="D185">
-        <v>884185</v>
+        <v>1902</v>
       </c>
       <c r="E185">
-        <v>263343.0282674861</v>
+        <v>567.7188036343344</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -3539,16 +3539,16 @@
         <v>84</v>
       </c>
       <c r="B186">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C186">
-        <v>950.7</v>
+        <v>190.6</v>
       </c>
       <c r="D186">
-        <v>7305</v>
+        <v>1001</v>
       </c>
       <c r="E186">
-        <v>2153.376978143865</v>
+        <v>281.1267329870996</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -3559,13 +3559,13 @@
         <v>0</v>
       </c>
       <c r="C187">
-        <v>660.6</v>
+        <v>60.3</v>
       </c>
       <c r="D187">
-        <v>5304</v>
+        <v>201</v>
       </c>
       <c r="E187">
-        <v>1554.351774856644</v>
+        <v>80.40031094467234</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -3576,13 +3576,13 @@
         <v>0</v>
       </c>
       <c r="C188">
-        <v>90.09999999999999</v>
+        <v>20</v>
       </c>
       <c r="D188">
-        <v>501</v>
+        <v>100</v>
       </c>
       <c r="E188">
-        <v>144.8519589097779</v>
+        <v>40</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -3593,13 +3593,13 @@
         <v>0</v>
       </c>
       <c r="C189">
-        <v>370.4</v>
+        <v>20.1</v>
       </c>
       <c r="D189">
-        <v>1101</v>
+        <v>201</v>
       </c>
       <c r="E189">
-        <v>438.7530512714413</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -3610,13 +3610,13 @@
         <v>0</v>
       </c>
       <c r="C190">
-        <v>150.2</v>
+        <v>10</v>
       </c>
       <c r="D190">
-        <v>1001</v>
+        <v>100</v>
       </c>
       <c r="E190">
-        <v>290.9985566974517</v>
+        <v>30</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -3627,13 +3627,13 @@
         <v>0</v>
       </c>
       <c r="C191">
-        <v>90.3</v>
+        <v>110.2</v>
       </c>
       <c r="D191">
-        <v>301</v>
+        <v>901</v>
       </c>
       <c r="E191">
-        <v>104.8151229546576</v>
+        <v>270.3260253841646</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -3644,13 +3644,13 @@
         <v>0</v>
       </c>
       <c r="C192">
-        <v>10</v>
+        <v>190.5</v>
       </c>
       <c r="D192">
-        <v>100</v>
+        <v>1503</v>
       </c>
       <c r="E192">
-        <v>30</v>
+        <v>444.6243920434416</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -3661,13 +3661,13 @@
         <v>0</v>
       </c>
       <c r="C193">
-        <v>40.2</v>
+        <v>390.7</v>
       </c>
       <c r="D193">
-        <v>201</v>
+        <v>1402</v>
       </c>
       <c r="E193">
-        <v>66.66453329919891</v>
+        <v>503.4028307429349</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -3678,13 +3678,13 @@
         <v>0</v>
       </c>
       <c r="C194">
-        <v>10</v>
+        <v>20.1</v>
       </c>
       <c r="D194">
-        <v>100</v>
+        <v>201</v>
       </c>
       <c r="E194">
-        <v>30</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -3695,13 +3695,13 @@
         <v>0</v>
       </c>
       <c r="C195">
-        <v>50.2</v>
+        <v>10.1</v>
       </c>
       <c r="D195">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="E195">
-        <v>80.99481464884033</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -3712,13 +3712,13 @@
         <v>0</v>
       </c>
       <c r="C196">
-        <v>120.2</v>
+        <v>50.2</v>
       </c>
       <c r="D196">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="E196">
-        <v>299.6533997804797</v>
+        <v>80.99481464884033</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -3729,13 +3729,13 @@
         <v>0</v>
       </c>
       <c r="C197">
-        <v>30.1</v>
+        <v>720.6</v>
       </c>
       <c r="D197">
-        <v>201</v>
+        <v>6404</v>
       </c>
       <c r="E197">
-        <v>64.29688950485863</v>
+        <v>1898.930604313912</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -3746,13 +3746,13 @@
         <v>0</v>
       </c>
       <c r="C198">
-        <v>20.1</v>
+        <v>40.2</v>
       </c>
       <c r="D198">
         <v>201</v>
       </c>
       <c r="E198">
-        <v>60.3</v>
+        <v>66.66453329919891</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -3763,13 +3763,13 @@
         <v>0</v>
       </c>
       <c r="C199">
-        <v>230.3</v>
+        <v>130.2</v>
       </c>
       <c r="D199">
-        <v>1001</v>
+        <v>901</v>
       </c>
       <c r="E199">
-        <v>390.3872564518468</v>
+        <v>265.081421453862</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -3780,13 +3780,13 @@
         <v>0</v>
       </c>
       <c r="C200">
-        <v>30.2</v>
+        <v>50.2</v>
       </c>
       <c r="D200">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E200">
-        <v>64.5628376080234</v>
+        <v>80.99481464884033</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -3797,13 +3797,13 @@
         <v>0</v>
       </c>
       <c r="C201">
-        <v>68887042.90000001</v>
+        <v>35037374.5</v>
       </c>
       <c r="D201">
-        <v>162342236</v>
+        <v>113906179</v>
       </c>
       <c r="E201">
-        <v>54100853.77534308</v>
+        <v>38733126.07452082</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -3814,13 +3814,13 @@
         <v>0</v>
       </c>
       <c r="C202">
-        <v>8032183.8</v>
+        <v>8190556.7</v>
       </c>
       <c r="D202">
-        <v>33231029</v>
+        <v>21272971</v>
       </c>
       <c r="E202">
-        <v>10767651.01988807</v>
+        <v>6860077.235073875</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -3831,13 +3831,13 @@
         <v>0</v>
       </c>
       <c r="C203">
-        <v>1087294.1</v>
+        <v>2746756.1</v>
       </c>
       <c r="D203">
-        <v>5037597</v>
+        <v>8190401</v>
       </c>
       <c r="E203">
-        <v>1515402.506050155</v>
+        <v>2815699.21268478</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -3848,13 +3848,13 @@
         <v>0</v>
       </c>
       <c r="C204">
-        <v>163409.8</v>
+        <v>632839.7</v>
       </c>
       <c r="D204">
-        <v>414549</v>
+        <v>2057121</v>
       </c>
       <c r="E204">
-        <v>199910.0370780817</v>
+        <v>656155.0653077442</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -3865,13 +3865,13 @@
         <v>0</v>
       </c>
       <c r="C205">
-        <v>40625.5</v>
+        <v>176268.5</v>
       </c>
       <c r="D205">
-        <v>401849</v>
+        <v>702765</v>
       </c>
       <c r="E205">
-        <v>120410.2017739776</v>
+        <v>278501.9054574852</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -3882,13 +3882,13 @@
         <v>0</v>
       </c>
       <c r="C206">
-        <v>110.5</v>
+        <v>50.3</v>
       </c>
       <c r="D206">
-        <v>501</v>
+        <v>201</v>
       </c>
       <c r="E206">
-        <v>151.6912983661225</v>
+        <v>81.05683191440434</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -3899,13 +3899,13 @@
         <v>0</v>
       </c>
       <c r="C207">
-        <v>40.3</v>
+        <v>130.2</v>
       </c>
       <c r="D207">
-        <v>302</v>
+        <v>1001</v>
       </c>
       <c r="E207">
-        <v>92.28439738113913</v>
+        <v>297.133236107979</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -3916,13 +3916,13 @@
         <v>0</v>
       </c>
       <c r="C208">
-        <v>140.3</v>
+        <v>50.2</v>
       </c>
       <c r="D208">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="E208">
-        <v>310.9283036328472</v>
+        <v>80.99481464884033</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -3933,13 +3933,13 @@
         <v>0</v>
       </c>
       <c r="C209">
-        <v>100.1</v>
+        <v>0</v>
       </c>
       <c r="D209">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="E209">
-        <v>300.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -3950,13 +3950,13 @@
         <v>0</v>
       </c>
       <c r="C210">
-        <v>50.3</v>
+        <v>0</v>
       </c>
       <c r="D210">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="E210">
-        <v>121.0388780516409</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -3967,13 +3967,13 @@
         <v>0</v>
       </c>
       <c r="C211">
-        <v>230.3</v>
+        <v>50.2</v>
       </c>
       <c r="D211">
-        <v>1402</v>
+        <v>201</v>
       </c>
       <c r="E211">
-        <v>474.0278578311617</v>
+        <v>80.99481464884033</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -3984,13 +3984,13 @@
         <v>0</v>
       </c>
       <c r="C212">
-        <v>10.1</v>
+        <v>200.2</v>
       </c>
       <c r="D212">
-        <v>101</v>
+        <v>1001</v>
       </c>
       <c r="E212">
-        <v>30.3</v>
+        <v>400.4</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -4001,13 +4001,13 @@
         <v>0</v>
       </c>
       <c r="C213">
-        <v>210.3</v>
+        <v>10.1</v>
       </c>
       <c r="D213">
-        <v>1701</v>
+        <v>101</v>
       </c>
       <c r="E213">
-        <v>503.1840716874889</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -4018,13 +4018,13 @@
         <v>0</v>
       </c>
       <c r="C214">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="D214">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="E214">
-        <v>64.40621088062859</v>
+        <v>46.28401451905398</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -4052,13 +4052,13 @@
         <v>0</v>
       </c>
       <c r="C216">
-        <v>60.3</v>
+        <v>100.1</v>
       </c>
       <c r="D216">
-        <v>302</v>
+        <v>901</v>
       </c>
       <c r="E216">
-        <v>102.588547119062</v>
+        <v>268.6263017651101</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -4069,13 +4069,13 @@
         <v>0</v>
       </c>
       <c r="C217">
-        <v>150.5</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D217">
         <v>901</v>
       </c>
       <c r="E217">
-        <v>269.7236548766163</v>
+        <v>270.3</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -4086,13 +4086,13 @@
         <v>0</v>
       </c>
       <c r="C218">
-        <v>680.6</v>
+        <v>160.3</v>
       </c>
       <c r="D218">
-        <v>6404</v>
+        <v>1402</v>
       </c>
       <c r="E218">
-        <v>1909.446370024568</v>
+        <v>418.2157457580956</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="C219">
-        <v>60.3</v>
+        <v>110.2</v>
       </c>
       <c r="D219">
-        <v>402</v>
+        <v>1102</v>
       </c>
       <c r="E219">
-        <v>128.7027971724002</v>
+        <v>330.6</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -4120,13 +4120,13 @@
         <v>0</v>
       </c>
       <c r="C220">
-        <v>20.1</v>
+        <v>130.3</v>
       </c>
       <c r="D220">
-        <v>201</v>
+        <v>901</v>
       </c>
       <c r="E220">
-        <v>60.3</v>
+        <v>268.8535102988242</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -4137,13 +4137,13 @@
         <v>0</v>
       </c>
       <c r="C221">
-        <v>66458641.5</v>
+        <v>56541146.5</v>
       </c>
       <c r="D221">
-        <v>216763121</v>
+        <v>159312167</v>
       </c>
       <c r="E221">
-        <v>60208033.85854971</v>
+        <v>43058661.39332537</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -4154,13 +4154,13 @@
         <v>0</v>
       </c>
       <c r="C222">
-        <v>30400879.5</v>
+        <v>20624281.5</v>
       </c>
       <c r="D222">
-        <v>113921774</v>
+        <v>65563594</v>
       </c>
       <c r="E222">
-        <v>32985984.681045</v>
+        <v>25246508.59508783</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -4171,13 +4171,13 @@
         <v>0</v>
       </c>
       <c r="C223">
-        <v>6760568.3</v>
+        <v>1334763.2</v>
       </c>
       <c r="D223">
-        <v>43264494</v>
+        <v>13347531</v>
       </c>
       <c r="E223">
-        <v>13998328.31286697</v>
+        <v>4004255.933446558</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -4188,13 +4188,13 @@
         <v>0</v>
       </c>
       <c r="C224">
-        <v>0</v>
+        <v>60.3</v>
       </c>
       <c r="D224">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="E224">
-        <v>0</v>
+        <v>92.10977146861238</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -4205,13 +4205,13 @@
         <v>0</v>
       </c>
       <c r="C225">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D225">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E225">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -4222,13 +4222,13 @@
         <v>0</v>
       </c>
       <c r="C226">
-        <v>120.3</v>
+        <v>30.2</v>
       </c>
       <c r="D226">
-        <v>1102</v>
+        <v>201</v>
       </c>
       <c r="E226">
-        <v>328.6159004065385</v>
+        <v>64.40621088062859</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -4239,13 +4239,13 @@
         <v>0</v>
       </c>
       <c r="C227">
-        <v>120.2</v>
+        <v>20.1</v>
       </c>
       <c r="D227">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="E227">
-        <v>299.6533997804797</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -4256,13 +4256,13 @@
         <v>0</v>
       </c>
       <c r="C228">
-        <v>20.1</v>
+        <v>60.3</v>
       </c>
       <c r="D228">
         <v>201</v>
       </c>
       <c r="E228">
-        <v>60.3</v>
+        <v>92.10977146861238</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -4273,13 +4273,13 @@
         <v>0</v>
       </c>
       <c r="C229">
-        <v>120.2</v>
+        <v>250.5</v>
       </c>
       <c r="D229">
-        <v>901</v>
+        <v>1001</v>
       </c>
       <c r="E229">
-        <v>267.903266124174</v>
+        <v>383.0799524903385</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -4290,13 +4290,13 @@
         <v>0</v>
       </c>
       <c r="C230">
-        <v>170.5</v>
+        <v>90.5</v>
       </c>
       <c r="D230">
-        <v>1302</v>
+        <v>302</v>
       </c>
       <c r="E230">
-        <v>385.4486347102555</v>
+        <v>114.2385661674725</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -4307,13 +4307,13 @@
         <v>0</v>
       </c>
       <c r="C231">
-        <v>30.1</v>
+        <v>90.5</v>
       </c>
       <c r="D231">
-        <v>201</v>
+        <v>302</v>
       </c>
       <c r="E231">
-        <v>64.29688950485864</v>
+        <v>114.2385661674725</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -4324,13 +4324,13 @@
         <v>0</v>
       </c>
       <c r="C232">
-        <v>60.3</v>
+        <v>40.2</v>
       </c>
       <c r="D232">
         <v>201</v>
       </c>
       <c r="E232">
-        <v>92.10977146861238</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -4341,13 +4341,13 @@
         <v>0</v>
       </c>
       <c r="C233">
-        <v>50.3</v>
+        <v>10</v>
       </c>
       <c r="D233">
-        <v>402</v>
+        <v>100</v>
       </c>
       <c r="E233">
-        <v>121.0388780516409</v>
+        <v>30</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -4358,13 +4358,13 @@
         <v>0</v>
       </c>
       <c r="C234">
-        <v>730.6</v>
+        <v>40.2</v>
       </c>
       <c r="D234">
-        <v>6804</v>
+        <v>201</v>
       </c>
       <c r="E234">
-        <v>2025.518560764132</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -4375,13 +4375,13 @@
         <v>0</v>
       </c>
       <c r="C235">
-        <v>100.1</v>
+        <v>290.7</v>
       </c>
       <c r="D235">
-        <v>1001</v>
+        <v>2002</v>
       </c>
       <c r="E235">
-        <v>300.3</v>
+        <v>577.4899219899859</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -4392,13 +4392,13 @@
         <v>0</v>
       </c>
       <c r="C236">
-        <v>120.2</v>
+        <v>50.2</v>
       </c>
       <c r="D236">
-        <v>1001</v>
+        <v>301</v>
       </c>
       <c r="E236">
-        <v>299.6533997804797</v>
+        <v>102.8599047248246</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -4409,13 +4409,13 @@
         <v>0</v>
       </c>
       <c r="C237">
-        <v>40.2</v>
+        <v>100.1</v>
       </c>
       <c r="D237">
-        <v>201</v>
+        <v>1001</v>
       </c>
       <c r="E237">
-        <v>66.66453329919891</v>
+        <v>300.3</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -4426,13 +4426,13 @@
         <v>0</v>
       </c>
       <c r="C238">
-        <v>70.3</v>
+        <v>30.1</v>
       </c>
       <c r="D238">
         <v>201</v>
       </c>
       <c r="E238">
-        <v>90.43345619846671</v>
+        <v>64.29688950485864</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -4443,13 +4443,13 @@
         <v>0</v>
       </c>
       <c r="C239">
-        <v>0</v>
+        <v>50.3</v>
       </c>
       <c r="D239">
-        <v>0</v>
+        <v>402</v>
       </c>
       <c r="E239">
-        <v>0</v>
+        <v>121.0388780516409</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -4460,13 +4460,13 @@
         <v>0</v>
       </c>
       <c r="C240">
-        <v>20.1</v>
+        <v>760.8</v>
       </c>
       <c r="D240">
-        <v>201</v>
+        <v>7005</v>
       </c>
       <c r="E240">
-        <v>60.3</v>
+        <v>2083.340145055531</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -4477,13 +4477,13 @@
         <v>0</v>
       </c>
       <c r="C241">
-        <v>55634506.7</v>
+        <v>69578280</v>
       </c>
       <c r="D241">
-        <v>156800205</v>
+        <v>173865976</v>
       </c>
       <c r="E241">
-        <v>40368396.9885956</v>
+        <v>57806487.25984471</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -4494,13 +4494,13 @@
         <v>0</v>
       </c>
       <c r="C242">
-        <v>22843157.9</v>
+        <v>6296359.9</v>
       </c>
       <c r="D242">
-        <v>53585824</v>
+        <v>33115929</v>
       </c>
       <c r="E242">
-        <v>19326568.95657332</v>
+        <v>9984845.037581541</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -4511,13 +4511,13 @@
         <v>0</v>
       </c>
       <c r="C243">
-        <v>5270645.3</v>
+        <v>119477.9</v>
       </c>
       <c r="D243">
-        <v>16896285</v>
+        <v>531575</v>
       </c>
       <c r="E243">
-        <v>6869726.929385026</v>
+        <v>183393.9516164314</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -4528,13 +4528,13 @@
         <v>0</v>
       </c>
       <c r="C244">
-        <v>945929.3</v>
+        <v>13012.8</v>
       </c>
       <c r="D244">
-        <v>9454089</v>
+        <v>129726</v>
       </c>
       <c r="E244">
-        <v>2836053.287643589</v>
+        <v>38904.48076970055</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -4545,13 +4545,13 @@
         <v>0</v>
       </c>
       <c r="C245">
-        <v>0</v>
+        <v>180.5</v>
       </c>
       <c r="D245">
-        <v>0</v>
+        <v>901</v>
       </c>
       <c r="E245">
-        <v>0</v>
+        <v>264.1595162018586</v>
       </c>
     </row>
     <row r="246" spans="1:5">
@@ -4562,13 +4562,13 @@
         <v>0</v>
       </c>
       <c r="C246">
-        <v>150.4</v>
+        <v>110.2</v>
       </c>
       <c r="D246">
-        <v>1001</v>
+        <v>901</v>
       </c>
       <c r="E246">
-        <v>301.2315388534209</v>
+        <v>270.3260253841646</v>
       </c>
     </row>
     <row r="247" spans="1:5">
@@ -4579,13 +4579,13 @@
         <v>0</v>
       </c>
       <c r="C247">
-        <v>50.3</v>
+        <v>0</v>
       </c>
       <c r="D247">
-        <v>302</v>
+        <v>0</v>
       </c>
       <c r="E247">
-        <v>103.1038796554232</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248" spans="1:5">
@@ -4596,13 +4596,13 @@
         <v>0</v>
       </c>
       <c r="C248">
-        <v>40.2</v>
+        <v>150.4</v>
       </c>
       <c r="D248">
-        <v>201</v>
+        <v>1001</v>
       </c>
       <c r="E248">
-        <v>80.40000000000001</v>
+        <v>294.4150811354609</v>
       </c>
     </row>
     <row r="249" spans="1:5">
@@ -4613,13 +4613,13 @@
         <v>0</v>
       </c>
       <c r="C249">
-        <v>50.3</v>
+        <v>20.1</v>
       </c>
       <c r="D249">
         <v>201</v>
       </c>
       <c r="E249">
-        <v>81.05683191440434</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -4630,13 +4630,13 @@
         <v>0</v>
       </c>
       <c r="C250">
-        <v>60.4</v>
+        <v>20.1</v>
       </c>
       <c r="D250">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="E250">
-        <v>80.45023306367732</v>
+        <v>40.20062188573704</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -4647,13 +4647,13 @@
         <v>0</v>
       </c>
       <c r="C251">
-        <v>200.2</v>
+        <v>30.1</v>
       </c>
       <c r="D251">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="E251">
-        <v>377.2269343511939</v>
+        <v>64.29688950485864</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -4664,13 +4664,13 @@
         <v>0</v>
       </c>
       <c r="C252">
-        <v>20.2</v>
+        <v>30.3</v>
       </c>
       <c r="D252">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="E252">
-        <v>40.4</v>
+        <v>64.516742013217</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -4681,13 +4681,13 @@
         <v>0</v>
       </c>
       <c r="C253">
-        <v>130.3</v>
+        <v>660.5</v>
       </c>
       <c r="D253">
-        <v>901</v>
+        <v>6404</v>
       </c>
       <c r="E253">
-        <v>268.8535102988243</v>
+        <v>1915.437665391385</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -4698,13 +4698,13 @@
         <v>0</v>
       </c>
       <c r="C254">
-        <v>20.1</v>
+        <v>220.3</v>
       </c>
       <c r="D254">
-        <v>201</v>
+        <v>1001</v>
       </c>
       <c r="E254">
-        <v>60.3</v>
+        <v>394.8521368816433</v>
       </c>
     </row>
     <row r="255" spans="1:5">
@@ -4715,13 +4715,13 @@
         <v>0</v>
       </c>
       <c r="C255">
-        <v>260.4</v>
+        <v>130.2</v>
       </c>
       <c r="D255">
-        <v>1502</v>
+        <v>1001</v>
       </c>
       <c r="E255">
-        <v>492.9629194980085</v>
+        <v>297.133236107979</v>
       </c>
     </row>
     <row r="256" spans="1:5">
@@ -4732,13 +4732,13 @@
         <v>0</v>
       </c>
       <c r="C256">
-        <v>0</v>
+        <v>160.2</v>
       </c>
       <c r="D256">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="E256">
-        <v>0</v>
+        <v>307.5323722797326</v>
       </c>
     </row>
     <row r="257" spans="1:5">
@@ -4749,13 +4749,13 @@
         <v>0</v>
       </c>
       <c r="C257">
-        <v>110.4</v>
+        <v>30.1</v>
       </c>
       <c r="D257">
-        <v>400</v>
+        <v>201</v>
       </c>
       <c r="E257">
-        <v>144.9566831850122</v>
+        <v>64.29688950485864</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -4766,13 +4766,13 @@
         <v>0</v>
       </c>
       <c r="C258">
-        <v>50.2</v>
+        <v>120.2</v>
       </c>
       <c r="D258">
-        <v>201</v>
+        <v>901</v>
       </c>
       <c r="E258">
-        <v>67.38070940558582</v>
+        <v>267.903266124174</v>
       </c>
     </row>
     <row r="259" spans="1:5">
@@ -4783,13 +4783,13 @@
         <v>0</v>
       </c>
       <c r="C259">
-        <v>70.3</v>
+        <v>310.4</v>
       </c>
       <c r="D259">
-        <v>402</v>
+        <v>1001</v>
       </c>
       <c r="E259">
-        <v>119.3248088202952</v>
+        <v>435.0542954620722</v>
       </c>
     </row>
     <row r="260" spans="1:5">
@@ -4800,13 +4800,13 @@
         <v>0</v>
       </c>
       <c r="C260">
-        <v>160.4</v>
+        <v>140.3</v>
       </c>
       <c r="D260">
         <v>1001</v>
       </c>
       <c r="E260">
-        <v>294.2655943191457</v>
+        <v>297.651154877652</v>
       </c>
     </row>
     <row r="261" spans="1:5">
@@ -4817,13 +4817,13 @@
         <v>0</v>
       </c>
       <c r="C261">
-        <v>57694385.7</v>
+        <v>49630677.4</v>
       </c>
       <c r="D261">
-        <v>111837581</v>
+        <v>80818709</v>
       </c>
       <c r="E261">
-        <v>38164141.94642735</v>
+        <v>25797942.28656883</v>
       </c>
     </row>
     <row r="262" spans="1:5">
@@ -4834,13 +4834,13 @@
         <v>0</v>
       </c>
       <c r="C262">
-        <v>28241999.1</v>
+        <v>34519018.5</v>
       </c>
       <c r="D262">
-        <v>98176238</v>
+        <v>73133091</v>
       </c>
       <c r="E262">
-        <v>28778675.99757506</v>
+        <v>27170120.87825479</v>
       </c>
     </row>
     <row r="263" spans="1:5">
@@ -4851,13 +4851,13 @@
         <v>0</v>
       </c>
       <c r="C263">
-        <v>10494117.9</v>
+        <v>5541424.6</v>
       </c>
       <c r="D263">
-        <v>24443236</v>
+        <v>53553057</v>
       </c>
       <c r="E263">
-        <v>7594624.815260784</v>
+        <v>16007872.45030381</v>
       </c>
     </row>
     <row r="264" spans="1:5">
@@ -4868,13 +4868,13 @@
         <v>0</v>
       </c>
       <c r="C264">
-        <v>4613161.8</v>
+        <v>880.7</v>
       </c>
       <c r="D264">
-        <v>14016701</v>
+        <v>8305</v>
       </c>
       <c r="E264">
-        <v>5012303.630663007</v>
+        <v>2476.846828126439</v>
       </c>
     </row>
     <row r="265" spans="1:5">
@@ -4885,13 +4885,13 @@
         <v>0</v>
       </c>
       <c r="C265">
-        <v>8572.5</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D265">
-        <v>59421</v>
+        <v>901</v>
       </c>
       <c r="E265">
-        <v>18578.12983725757</v>
+        <v>270.3</v>
       </c>
     </row>
     <row r="266" spans="1:5">
@@ -4902,13 +4902,13 @@
         <v>0</v>
       </c>
       <c r="C266">
-        <v>80.40000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="D266">
         <v>302</v>
       </c>
       <c r="E266">
-        <v>108.3348512714168</v>
+        <v>92.21908696143115</v>
       </c>
     </row>
     <row r="267" spans="1:5">
@@ -4919,13 +4919,13 @@
         <v>0</v>
       </c>
       <c r="C267">
-        <v>40.1</v>
+        <v>200.3</v>
       </c>
       <c r="D267">
-        <v>201</v>
+        <v>1001</v>
       </c>
       <c r="E267">
-        <v>66.57394385193055</v>
+        <v>377.2004904556727</v>
       </c>
     </row>
     <row r="268" spans="1:5">
@@ -4936,13 +4936,13 @@
         <v>0</v>
       </c>
       <c r="C268">
-        <v>770.8</v>
+        <v>130.4</v>
       </c>
       <c r="D268">
-        <v>6804</v>
+        <v>901</v>
       </c>
       <c r="E268">
-        <v>2014.072828871886</v>
+        <v>265.0589368423559</v>
       </c>
     </row>
     <row r="269" spans="1:5">
@@ -4953,13 +4953,13 @@
         <v>0</v>
       </c>
       <c r="C269">
-        <v>150.3</v>
+        <v>230.5</v>
       </c>
       <c r="D269">
-        <v>901</v>
+        <v>1001</v>
       </c>
       <c r="E269">
-        <v>262.0500143102458</v>
+        <v>369.2836985300056</v>
       </c>
     </row>
     <row r="270" spans="1:5">
@@ -4970,13 +4970,13 @@
         <v>0</v>
       </c>
       <c r="C270">
-        <v>50.2</v>
+        <v>10.1</v>
       </c>
       <c r="D270">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="E270">
-        <v>80.99481464884033</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="271" spans="1:5">
@@ -4987,13 +4987,13 @@
         <v>0</v>
       </c>
       <c r="C271">
-        <v>30.1</v>
+        <v>40.2</v>
       </c>
       <c r="D271">
         <v>201</v>
       </c>
       <c r="E271">
-        <v>64.29688950485863</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="272" spans="1:5">
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="C272">
-        <v>880.6</v>
+        <v>200.3</v>
       </c>
       <c r="D272">
-        <v>7705</v>
+        <v>1001</v>
       </c>
       <c r="E272">
-        <v>2298.361642561936</v>
+        <v>377.2004904556727</v>
       </c>
     </row>
     <row r="273" spans="1:5">
@@ -5021,13 +5021,13 @@
         <v>0</v>
       </c>
       <c r="C273">
-        <v>30.1</v>
+        <v>100.1</v>
       </c>
       <c r="D273">
-        <v>301</v>
+        <v>1001</v>
       </c>
       <c r="E273">
-        <v>90.3</v>
+        <v>300.3</v>
       </c>
     </row>
     <row r="274" spans="1:5">
@@ -5038,13 +5038,13 @@
         <v>0</v>
       </c>
       <c r="C274">
-        <v>110.1</v>
+        <v>100.1</v>
       </c>
       <c r="D274">
         <v>1001</v>
       </c>
       <c r="E274">
-        <v>298.4595282446181</v>
+        <v>300.3</v>
       </c>
     </row>
     <row r="275" spans="1:5">
@@ -5055,13 +5055,13 @@
         <v>0</v>
       </c>
       <c r="C275">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
       <c r="D275">
         <v>201</v>
       </c>
       <c r="E275">
-        <v>80.99481464884033</v>
+        <v>67.30594327397841</v>
       </c>
     </row>
     <row r="276" spans="1:5">
@@ -5072,13 +5072,13 @@
         <v>0</v>
       </c>
       <c r="C276">
-        <v>50.2</v>
+        <v>20.1</v>
       </c>
       <c r="D276">
         <v>201</v>
       </c>
       <c r="E276">
-        <v>80.99481464884033</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="277" spans="1:5">
@@ -5089,13 +5089,13 @@
         <v>0</v>
       </c>
       <c r="C277">
-        <v>20.1</v>
+        <v>30.1</v>
       </c>
       <c r="D277">
         <v>201</v>
       </c>
       <c r="E277">
-        <v>60.3</v>
+        <v>64.29688950485863</v>
       </c>
     </row>
     <row r="278" spans="1:5">
@@ -5106,13 +5106,13 @@
         <v>0</v>
       </c>
       <c r="C278">
-        <v>130.2</v>
+        <v>20.1</v>
       </c>
       <c r="D278">
-        <v>1302</v>
+        <v>101</v>
       </c>
       <c r="E278">
-        <v>390.6</v>
+        <v>40.20062188573704</v>
       </c>
     </row>
     <row r="279" spans="1:5">
@@ -5123,13 +5123,13 @@
         <v>0</v>
       </c>
       <c r="C279">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="D279">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E279">
-        <v>30</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="280" spans="1:5">
@@ -5140,13 +5140,13 @@
         <v>0</v>
       </c>
       <c r="C280">
-        <v>0</v>
+        <v>70.5</v>
       </c>
       <c r="D280">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="E280">
-        <v>0</v>
+        <v>90.50110496563012</v>
       </c>
     </row>
     <row r="281" spans="1:5">
@@ -5157,13 +5157,13 @@
         <v>0</v>
       </c>
       <c r="C281">
-        <v>94482037.90000001</v>
+        <v>73552480.7</v>
       </c>
       <c r="D281">
-        <v>264812702</v>
+        <v>143730145</v>
       </c>
       <c r="E281">
-        <v>78660341.51259764</v>
+        <v>39631001.86511517</v>
       </c>
     </row>
     <row r="282" spans="1:5">
@@ -5174,13 +5174,13 @@
         <v>0</v>
       </c>
       <c r="C282">
-        <v>33123300.8</v>
+        <v>27667839.4</v>
       </c>
       <c r="D282">
-        <v>122201215</v>
+        <v>53857255</v>
       </c>
       <c r="E282">
-        <v>44073512.44841539</v>
+        <v>19854298.96850707</v>
       </c>
     </row>
     <row r="283" spans="1:5">
@@ -5191,13 +5191,13 @@
         <v>0</v>
       </c>
       <c r="C283">
-        <v>15639774.8</v>
+        <v>13450526.3</v>
       </c>
       <c r="D283">
-        <v>118536858</v>
+        <v>26064586</v>
       </c>
       <c r="E283">
-        <v>34557786.73659282</v>
+        <v>8673489.206439609</v>
       </c>
     </row>
     <row r="284" spans="1:5">
@@ -5208,13 +5208,13 @@
         <v>0</v>
       </c>
       <c r="C284">
-        <v>2639046.7</v>
+        <v>4728664.2</v>
       </c>
       <c r="D284">
-        <v>8807463</v>
+        <v>26260154</v>
       </c>
       <c r="E284">
-        <v>3872711.726281161</v>
+        <v>8251738.609563415</v>
       </c>
     </row>
     <row r="285" spans="1:5">
@@ -5225,13 +5225,13 @@
         <v>0</v>
       </c>
       <c r="C285">
-        <v>120.6</v>
+        <v>51978.2</v>
       </c>
       <c r="D285">
-        <v>402</v>
+        <v>230940</v>
       </c>
       <c r="E285">
-        <v>133.3283165722871</v>
+        <v>91073.62540801811</v>
       </c>
     </row>
     <row r="286" spans="1:5">
@@ -5242,13 +5242,13 @@
         <v>0</v>
       </c>
       <c r="C286">
-        <v>130.2</v>
+        <v>5810.2</v>
       </c>
       <c r="D286">
-        <v>1001</v>
+        <v>57801</v>
       </c>
       <c r="E286">
-        <v>297.133236107979</v>
+        <v>17330.49901647382</v>
       </c>
     </row>
     <row r="287" spans="1:5">
@@ -5259,13 +5259,13 @@
         <v>0</v>
       </c>
       <c r="C287">
-        <v>120.2</v>
+        <v>60</v>
       </c>
       <c r="D287">
-        <v>901</v>
+        <v>400</v>
       </c>
       <c r="E287">
-        <v>267.903266124174</v>
+        <v>120</v>
       </c>
     </row>
     <row r="288" spans="1:5">
@@ -5276,13 +5276,13 @@
         <v>0</v>
       </c>
       <c r="C288">
-        <v>140.3</v>
+        <v>20.1</v>
       </c>
       <c r="D288">
-        <v>1001</v>
+        <v>101</v>
       </c>
       <c r="E288">
-        <v>294.2383557594081</v>
+        <v>40.20062188573705</v>
       </c>
     </row>
     <row r="289" spans="1:5">
@@ -5293,13 +5293,13 @@
         <v>0</v>
       </c>
       <c r="C289">
-        <v>70.40000000000001</v>
+        <v>700.6</v>
       </c>
       <c r="D289">
-        <v>302</v>
+        <v>6905</v>
       </c>
       <c r="E289">
-        <v>110.654597735476</v>
+        <v>2068.352542483993</v>
       </c>
     </row>
     <row r="290" spans="1:5">
@@ -5310,13 +5310,13 @@
         <v>0</v>
       </c>
       <c r="C290">
-        <v>0</v>
+        <v>100.4</v>
       </c>
       <c r="D290">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E290">
-        <v>0</v>
+        <v>126.6500690880191</v>
       </c>
     </row>
     <row r="291" spans="1:5">
@@ -5327,13 +5327,13 @@
         <v>0</v>
       </c>
       <c r="C291">
-        <v>10.1</v>
+        <v>30.2</v>
       </c>
       <c r="D291">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="E291">
-        <v>30.3</v>
+        <v>64.40621088062859</v>
       </c>
     </row>
     <row r="292" spans="1:5">
@@ -5344,13 +5344,13 @@
         <v>0</v>
       </c>
       <c r="C292">
-        <v>30.1</v>
+        <v>50.2</v>
       </c>
       <c r="D292">
-        <v>201</v>
+        <v>301</v>
       </c>
       <c r="E292">
-        <v>64.29688950485863</v>
+        <v>102.8599047248246</v>
       </c>
     </row>
     <row r="293" spans="1:5">
@@ -5361,13 +5361,13 @@
         <v>0</v>
       </c>
       <c r="C293">
-        <v>50</v>
+        <v>100.1</v>
       </c>
       <c r="D293">
-        <v>400</v>
+        <v>1001</v>
       </c>
       <c r="E293">
-        <v>120.415945787923</v>
+        <v>300.3</v>
       </c>
     </row>
     <row r="294" spans="1:5">
@@ -5378,13 +5378,13 @@
         <v>0</v>
       </c>
       <c r="C294">
-        <v>160.4</v>
+        <v>50.3</v>
       </c>
       <c r="D294">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="E294">
-        <v>307.6888688269369</v>
+        <v>81.05683191440434</v>
       </c>
     </row>
     <row r="295" spans="1:5">
@@ -5395,13 +5395,13 @@
         <v>0</v>
       </c>
       <c r="C295">
-        <v>50.3</v>
+        <v>10</v>
       </c>
       <c r="D295">
-        <v>302</v>
+        <v>100</v>
       </c>
       <c r="E295">
-        <v>92.79229493875016</v>
+        <v>30</v>
       </c>
     </row>
     <row r="296" spans="1:5">
@@ -5412,13 +5412,13 @@
         <v>0</v>
       </c>
       <c r="C296">
-        <v>110.2</v>
+        <v>30.2</v>
       </c>
       <c r="D296">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="E296">
-        <v>298.456294957905</v>
+        <v>64.40621088062858</v>
       </c>
     </row>
     <row r="297" spans="1:5">
@@ -5446,13 +5446,13 @@
         <v>0</v>
       </c>
       <c r="C298">
-        <v>40.1</v>
+        <v>20.1</v>
       </c>
       <c r="D298">
         <v>201</v>
       </c>
       <c r="E298">
-        <v>66.57394385193055</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="299" spans="1:5">
@@ -5463,13 +5463,13 @@
         <v>0</v>
       </c>
       <c r="C299">
-        <v>30.1</v>
+        <v>20.1</v>
       </c>
       <c r="D299">
         <v>201</v>
       </c>
       <c r="E299">
-        <v>64.29688950485864</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="300" spans="1:5">
@@ -5480,13 +5480,13 @@
         <v>0</v>
       </c>
       <c r="C300">
-        <v>690.4</v>
+        <v>10.1</v>
       </c>
       <c r="D300">
-        <v>6804</v>
+        <v>101</v>
       </c>
       <c r="E300">
-        <v>2038.084747992585</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="301" spans="1:5">
@@ -5497,13 +5497,13 @@
         <v>0</v>
       </c>
       <c r="C301">
-        <v>66436045</v>
+        <v>52831980.3</v>
       </c>
       <c r="D301">
-        <v>175838544</v>
+        <v>125002825</v>
       </c>
       <c r="E301">
-        <v>55462694.57096995</v>
+        <v>36547594.46509536</v>
       </c>
     </row>
     <row r="302" spans="1:5">
@@ -5514,13 +5514,13 @@
         <v>0</v>
       </c>
       <c r="C302">
-        <v>25833971</v>
+        <v>29076926.7</v>
       </c>
       <c r="D302">
-        <v>71050778</v>
+        <v>59270493</v>
       </c>
       <c r="E302">
-        <v>24468025.88613791</v>
+        <v>18558996.92354829</v>
       </c>
     </row>
     <row r="303" spans="1:5">
@@ -5531,13 +5531,13 @@
         <v>0</v>
       </c>
       <c r="C303">
-        <v>11055661.6</v>
+        <v>17694896.7</v>
       </c>
       <c r="D303">
-        <v>52478294</v>
+        <v>29677169</v>
       </c>
       <c r="E303">
-        <v>14823292.69412955</v>
+        <v>12058894.33807832</v>
       </c>
     </row>
     <row r="304" spans="1:5">
@@ -5548,13 +5548,13 @@
         <v>0</v>
       </c>
       <c r="C304">
-        <v>2503824.2</v>
+        <v>13187566.1</v>
       </c>
       <c r="D304">
-        <v>7569562</v>
+        <v>29514269</v>
       </c>
       <c r="E304">
-        <v>2936202.160190568</v>
+        <v>11094389.5637535</v>
       </c>
     </row>
     <row r="305" spans="1:5">
@@ -5565,13 +5565,13 @@
         <v>0</v>
       </c>
       <c r="C305">
-        <v>87701.39999999999</v>
+        <v>5081284.1</v>
       </c>
       <c r="D305">
-        <v>403551</v>
+        <v>21087989</v>
       </c>
       <c r="E305">
-        <v>155455.1252376067</v>
+        <v>7033938.701890207</v>
       </c>
     </row>
     <row r="306" spans="1:5">
@@ -5582,13 +5582,13 @@
         <v>0</v>
       </c>
       <c r="C306">
-        <v>580.6</v>
+        <v>3280.2</v>
       </c>
       <c r="D306">
-        <v>1802</v>
+        <v>32400</v>
       </c>
       <c r="E306">
-        <v>623.237065649982</v>
+        <v>9706.92372278674</v>
       </c>
     </row>
     <row r="307" spans="1:5">
@@ -5599,13 +5599,13 @@
         <v>0</v>
       </c>
       <c r="C307">
-        <v>20.2</v>
+        <v>50.3</v>
       </c>
       <c r="D307">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E307">
-        <v>60.6</v>
+        <v>81.05683191440434</v>
       </c>
     </row>
     <row r="308" spans="1:5">
@@ -5616,13 +5616,13 @@
         <v>0</v>
       </c>
       <c r="C308">
-        <v>40.2</v>
+        <v>130.2</v>
       </c>
       <c r="D308">
-        <v>201</v>
+        <v>1101</v>
       </c>
       <c r="E308">
-        <v>80.40000000000001</v>
+        <v>329.1020510419222</v>
       </c>
     </row>
     <row r="309" spans="1:5">
@@ -5633,13 +5633,13 @@
         <v>0</v>
       </c>
       <c r="C309">
-        <v>160.4</v>
+        <v>400.6</v>
       </c>
       <c r="D309">
-        <v>1001</v>
+        <v>1802</v>
       </c>
       <c r="E309">
-        <v>294.2655943191456</v>
+        <v>705.0110921113228</v>
       </c>
     </row>
     <row r="310" spans="1:5">
@@ -5650,13 +5650,13 @@
         <v>0</v>
       </c>
       <c r="C310">
-        <v>160.4</v>
+        <v>250.4</v>
       </c>
       <c r="D310">
-        <v>1001</v>
+        <v>1101</v>
       </c>
       <c r="E310">
-        <v>294.2655943191457</v>
+        <v>408.4118509544012</v>
       </c>
     </row>
     <row r="311" spans="1:5">
@@ -5667,13 +5667,13 @@
         <v>0</v>
       </c>
       <c r="C311">
-        <v>0</v>
+        <v>40.2</v>
       </c>
       <c r="D311">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="E311">
-        <v>0</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="312" spans="1:5">
@@ -5684,13 +5684,13 @@
         <v>0</v>
       </c>
       <c r="C312">
-        <v>5981.9</v>
+        <v>170.2</v>
       </c>
       <c r="D312">
-        <v>59216</v>
+        <v>901</v>
       </c>
       <c r="E312">
-        <v>17744.92767779007</v>
+        <v>300.5530901521394</v>
       </c>
     </row>
     <row r="313" spans="1:5">
@@ -5701,13 +5701,13 @@
         <v>0</v>
       </c>
       <c r="C313">
-        <v>1131</v>
+        <v>40.1</v>
       </c>
       <c r="D313">
-        <v>8605</v>
+        <v>201</v>
       </c>
       <c r="E313">
-        <v>2517.729532733808</v>
+        <v>66.57394385193055</v>
       </c>
     </row>
     <row r="314" spans="1:5">
@@ -5718,13 +5718,13 @@
         <v>0</v>
       </c>
       <c r="C314">
-        <v>50.2</v>
+        <v>40.2</v>
       </c>
       <c r="D314">
         <v>201</v>
       </c>
       <c r="E314">
-        <v>80.99481464884033</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="315" spans="1:5">
@@ -5735,13 +5735,13 @@
         <v>0</v>
       </c>
       <c r="C315">
-        <v>60.2</v>
+        <v>10.1</v>
       </c>
       <c r="D315">
-        <v>402</v>
+        <v>101</v>
       </c>
       <c r="E315">
-        <v>120.5668279420173</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="316" spans="1:5">
@@ -5752,13 +5752,13 @@
         <v>0</v>
       </c>
       <c r="C316">
-        <v>60.3</v>
+        <v>40.3</v>
       </c>
       <c r="D316">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="E316">
-        <v>80.40031094467234</v>
+        <v>49.35797807852344</v>
       </c>
     </row>
     <row r="317" spans="1:5">
@@ -5769,13 +5769,13 @@
         <v>0</v>
       </c>
       <c r="C317">
-        <v>720.6</v>
+        <v>120.2</v>
       </c>
       <c r="D317">
-        <v>6804</v>
+        <v>1001</v>
       </c>
       <c r="E317">
-        <v>2028.851261182051</v>
+        <v>299.6533997804797</v>
       </c>
     </row>
     <row r="318" spans="1:5">
@@ -5786,13 +5786,13 @@
         <v>0</v>
       </c>
       <c r="C318">
-        <v>20.1</v>
+        <v>150.3</v>
       </c>
       <c r="D318">
-        <v>101</v>
+        <v>1402</v>
       </c>
       <c r="E318">
-        <v>40.20062188573704</v>
+        <v>418.3185508676373</v>
       </c>
     </row>
     <row r="319" spans="1:5">
@@ -5803,13 +5803,13 @@
         <v>0</v>
       </c>
       <c r="C319">
-        <v>110.2</v>
+        <v>60.2</v>
       </c>
       <c r="D319">
-        <v>1001</v>
+        <v>301</v>
       </c>
       <c r="E319">
-        <v>298.456294957905</v>
+        <v>120.4</v>
       </c>
     </row>
     <row r="320" spans="1:5">
@@ -5820,13 +5820,13 @@
         <v>0</v>
       </c>
       <c r="C320">
-        <v>50.3</v>
+        <v>170.5</v>
       </c>
       <c r="D320">
-        <v>201</v>
+        <v>1001</v>
       </c>
       <c r="E320">
-        <v>81.05683191440434</v>
+        <v>297.2043909500666</v>
       </c>
     </row>
     <row r="321" spans="1:5">
@@ -5837,13 +5837,13 @@
         <v>0</v>
       </c>
       <c r="C321">
-        <v>70025107.5</v>
+        <v>64601999.1</v>
       </c>
       <c r="D321">
-        <v>155549509</v>
+        <v>125516030</v>
       </c>
       <c r="E321">
-        <v>45914894.65022731</v>
+        <v>35718873.15442096</v>
       </c>
     </row>
     <row r="322" spans="1:5">
@@ -5854,13 +5854,13 @@
         <v>0</v>
       </c>
       <c r="C322">
-        <v>9905035.9</v>
+        <v>42690167.2</v>
       </c>
       <c r="D322">
-        <v>45091290</v>
+        <v>103050007</v>
       </c>
       <c r="E322">
-        <v>17006432.2775478</v>
+        <v>35565826.97433238</v>
       </c>
     </row>
     <row r="323" spans="1:5">
@@ -5871,13 +5871,13 @@
         <v>0</v>
       </c>
       <c r="C323">
-        <v>730.7</v>
+        <v>15343122.5</v>
       </c>
       <c r="D323">
-        <v>6804</v>
+        <v>94723958</v>
       </c>
       <c r="E323">
-        <v>2025.98603400912</v>
+        <v>27895197.81076097</v>
       </c>
     </row>
     <row r="324" spans="1:5">
@@ -5888,13 +5888,13 @@
         <v>0</v>
       </c>
       <c r="C324">
-        <v>20.1</v>
+        <v>2631.3</v>
       </c>
       <c r="D324">
-        <v>101</v>
+        <v>24110</v>
       </c>
       <c r="E324">
-        <v>40.20062188573705</v>
+        <v>7170.070474549048</v>
       </c>
     </row>
     <row r="325" spans="1:5">
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="C325">
-        <v>60.3</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D325">
-        <v>302</v>
+        <v>901</v>
       </c>
       <c r="E325">
-        <v>102.588547119062</v>
+        <v>270.3</v>
       </c>
     </row>
     <row r="326" spans="1:5">
@@ -5922,13 +5922,13 @@
         <v>0</v>
       </c>
       <c r="C326">
-        <v>70.3</v>
+        <v>30.1</v>
       </c>
       <c r="D326">
         <v>201</v>
       </c>
       <c r="E326">
-        <v>78.47426329695615</v>
+        <v>64.29688950485863</v>
       </c>
     </row>
     <row r="327" spans="1:5">
@@ -5939,13 +5939,13 @@
         <v>0</v>
       </c>
       <c r="C327">
-        <v>40.2</v>
+        <v>50.3</v>
       </c>
       <c r="D327">
         <v>201</v>
       </c>
       <c r="E327">
-        <v>66.66453329919891</v>
+        <v>81.05683191440434</v>
       </c>
     </row>
     <row r="328" spans="1:5">
@@ -5956,13 +5956,13 @@
         <v>0</v>
       </c>
       <c r="C328">
-        <v>0</v>
+        <v>150.3</v>
       </c>
       <c r="D328">
-        <v>0</v>
+        <v>1302</v>
       </c>
       <c r="E328">
-        <v>0</v>
+        <v>385.9409410777768</v>
       </c>
     </row>
     <row r="329" spans="1:5">
@@ -5973,13 +5973,13 @@
         <v>0</v>
       </c>
       <c r="C329">
-        <v>20.1</v>
+        <v>40.3</v>
       </c>
       <c r="D329">
-        <v>201</v>
+        <v>302</v>
       </c>
       <c r="E329">
-        <v>60.3</v>
+        <v>92.28439738113913</v>
       </c>
     </row>
     <row r="330" spans="1:5">
@@ -5990,13 +5990,13 @@
         <v>0</v>
       </c>
       <c r="C330">
-        <v>10</v>
+        <v>120.2</v>
       </c>
       <c r="D330">
-        <v>100</v>
+        <v>1001</v>
       </c>
       <c r="E330">
-        <v>30</v>
+        <v>299.6533997804797</v>
       </c>
     </row>
     <row r="331" spans="1:5">
@@ -6007,13 +6007,13 @@
         <v>0</v>
       </c>
       <c r="C331">
-        <v>120.3</v>
+        <v>120.2</v>
       </c>
       <c r="D331">
-        <v>901</v>
+        <v>1001</v>
       </c>
       <c r="E331">
-        <v>267.8958939588287</v>
+        <v>299.6533997804797</v>
       </c>
     </row>
     <row r="332" spans="1:5">
@@ -6024,13 +6024,13 @@
         <v>0</v>
       </c>
       <c r="C332">
-        <v>110.2</v>
+        <v>50.2</v>
       </c>
       <c r="D332">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="E332">
-        <v>298.456294957905</v>
+        <v>80.99481464884033</v>
       </c>
     </row>
     <row r="333" spans="1:5">
@@ -6041,13 +6041,13 @@
         <v>0</v>
       </c>
       <c r="C333">
-        <v>60.1</v>
+        <v>50.3</v>
       </c>
       <c r="D333">
-        <v>400</v>
+        <v>302</v>
       </c>
       <c r="E333">
-        <v>128.172110850996</v>
+        <v>103.1038796554232</v>
       </c>
     </row>
     <row r="334" spans="1:5">
@@ -6058,13 +6058,13 @@
         <v>0</v>
       </c>
       <c r="C334">
-        <v>20.1</v>
+        <v>30.1</v>
       </c>
       <c r="D334">
-        <v>201</v>
+        <v>301</v>
       </c>
       <c r="E334">
-        <v>60.3</v>
+        <v>90.29999999999998</v>
       </c>
     </row>
     <row r="335" spans="1:5">
@@ -6075,13 +6075,13 @@
         <v>0</v>
       </c>
       <c r="C335">
-        <v>130.3</v>
+        <v>40.3</v>
       </c>
       <c r="D335">
-        <v>1001</v>
+        <v>202</v>
       </c>
       <c r="E335">
-        <v>297.1232235958677</v>
+        <v>66.90597880608279</v>
       </c>
     </row>
     <row r="336" spans="1:5">
@@ -6092,13 +6092,13 @@
         <v>0</v>
       </c>
       <c r="C336">
-        <v>0</v>
+        <v>200.2</v>
       </c>
       <c r="D336">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="E336">
-        <v>0</v>
+        <v>400.4</v>
       </c>
     </row>
     <row r="337" spans="1:5">
@@ -6109,13 +6109,13 @@
         <v>0</v>
       </c>
       <c r="C337">
-        <v>120.2</v>
+        <v>50.2</v>
       </c>
       <c r="D337">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="E337">
-        <v>299.6533997804797</v>
+        <v>80.99481464884033</v>
       </c>
     </row>
     <row r="338" spans="1:5">
@@ -6126,13 +6126,13 @@
         <v>0</v>
       </c>
       <c r="C338">
-        <v>10.1</v>
+        <v>940.8</v>
       </c>
       <c r="D338">
-        <v>101</v>
+        <v>6804</v>
       </c>
       <c r="E338">
-        <v>30.3</v>
+        <v>2011.252733994413</v>
       </c>
     </row>
     <row r="339" spans="1:5">
@@ -6143,13 +6143,13 @@
         <v>0</v>
       </c>
       <c r="C339">
-        <v>140.3</v>
+        <v>230.4</v>
       </c>
       <c r="D339">
         <v>1001</v>
       </c>
       <c r="E339">
-        <v>297.6511548776521</v>
+        <v>390.353993190796</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -6160,13 +6160,13 @@
         <v>0</v>
       </c>
       <c r="C340">
-        <v>50.1</v>
+        <v>780.5</v>
       </c>
       <c r="D340">
-        <v>301</v>
+        <v>6804</v>
       </c>
       <c r="E340">
-        <v>92.46669670751736</v>
+        <v>2029.891979884644</v>
       </c>
     </row>
     <row r="341" spans="1:5">
@@ -6177,13 +6177,13 @@
         <v>0</v>
       </c>
       <c r="C341">
-        <v>92033995.59999999</v>
+        <v>73712939.2</v>
       </c>
       <c r="D341">
-        <v>234195187</v>
+        <v>122194452</v>
       </c>
       <c r="E341">
-        <v>75458517.79107819</v>
+        <v>43123470.15140209</v>
       </c>
     </row>
     <row r="342" spans="1:5">
@@ -6194,13 +6194,13 @@
         <v>0</v>
       </c>
       <c r="C342">
-        <v>40319215.5</v>
+        <v>52860759.6</v>
       </c>
       <c r="D342">
-        <v>148358026</v>
+        <v>103266120</v>
       </c>
       <c r="E342">
-        <v>53007939.20293134</v>
+        <v>40289988.43688785</v>
       </c>
     </row>
     <row r="343" spans="1:5">
@@ -6211,13 +6211,13 @@
         <v>0</v>
       </c>
       <c r="C343">
-        <v>10064600.2</v>
+        <v>20225570.6</v>
       </c>
       <c r="D343">
-        <v>71251015</v>
+        <v>62552786</v>
       </c>
       <c r="E343">
-        <v>20776087.32434452</v>
+        <v>25430294.88564138</v>
       </c>
     </row>
     <row r="344" spans="1:5">
@@ -6228,13 +6228,13 @@
         <v>0</v>
       </c>
       <c r="C344">
-        <v>1492041.1</v>
+        <v>40.1</v>
       </c>
       <c r="D344">
-        <v>9013669</v>
+        <v>201</v>
       </c>
       <c r="E344">
-        <v>2739355.250369526</v>
+        <v>66.57394385193055</v>
       </c>
     </row>
     <row r="345" spans="1:5">
@@ -6245,13 +6245,13 @@
         <v>0</v>
       </c>
       <c r="C345">
-        <v>11922.7</v>
+        <v>10.1</v>
       </c>
       <c r="D345">
-        <v>119026</v>
+        <v>101</v>
       </c>
       <c r="E345">
-        <v>35701.15029533362</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="346" spans="1:5">
@@ -6262,13 +6262,13 @@
         <v>0</v>
       </c>
       <c r="C346">
-        <v>60.4</v>
+        <v>10</v>
       </c>
       <c r="D346">
-        <v>201</v>
+        <v>100</v>
       </c>
       <c r="E346">
-        <v>80.45023306367732</v>
+        <v>30</v>
       </c>
     </row>
     <row r="347" spans="1:5">
@@ -6279,13 +6279,13 @@
         <v>0</v>
       </c>
       <c r="C347">
-        <v>140.4</v>
+        <v>20.1</v>
       </c>
       <c r="D347">
-        <v>1102</v>
+        <v>201</v>
       </c>
       <c r="E347">
-        <v>323.6795328716353</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="348" spans="1:5">
@@ -6296,13 +6296,13 @@
         <v>0</v>
       </c>
       <c r="C348">
-        <v>40.4</v>
+        <v>90.2</v>
       </c>
       <c r="D348">
-        <v>202</v>
+        <v>402</v>
       </c>
       <c r="E348">
-        <v>66.99582076517908</v>
+        <v>158.1908973360983</v>
       </c>
     </row>
     <row r="349" spans="1:5">
@@ -6313,13 +6313,13 @@
         <v>0</v>
       </c>
       <c r="C349">
-        <v>40.4</v>
+        <v>120.1</v>
       </c>
       <c r="D349">
-        <v>102</v>
+        <v>1001</v>
       </c>
       <c r="E349">
-        <v>49.48171379408761</v>
+        <v>296.2702988826251</v>
       </c>
     </row>
     <row r="350" spans="1:5">
@@ -6330,13 +6330,13 @@
         <v>0</v>
       </c>
       <c r="C350">
-        <v>40.1</v>
+        <v>690.5</v>
       </c>
       <c r="D350">
-        <v>201</v>
+        <v>6804</v>
       </c>
       <c r="E350">
-        <v>66.57394385193055</v>
+        <v>2038.055801493178</v>
       </c>
     </row>
     <row r="351" spans="1:5">
@@ -6347,13 +6347,13 @@
         <v>0</v>
       </c>
       <c r="C351">
-        <v>80.40000000000001</v>
+        <v>740.5</v>
       </c>
       <c r="D351">
-        <v>301</v>
+        <v>6404</v>
       </c>
       <c r="E351">
-        <v>108.1491562611563</v>
+        <v>1906.55748667592</v>
       </c>
     </row>
     <row r="352" spans="1:5">
@@ -6364,13 +6364,13 @@
         <v>0</v>
       </c>
       <c r="C352">
-        <v>40.2</v>
+        <v>100.1</v>
       </c>
       <c r="D352">
-        <v>201</v>
+        <v>1001</v>
       </c>
       <c r="E352">
-        <v>80.40000000000001</v>
+        <v>300.3</v>
       </c>
     </row>
     <row r="353" spans="1:5">
@@ -6381,13 +6381,13 @@
         <v>0</v>
       </c>
       <c r="C353">
-        <v>20.1</v>
+        <v>70.3</v>
       </c>
       <c r="D353">
-        <v>201</v>
+        <v>301</v>
       </c>
       <c r="E353">
-        <v>60.3</v>
+        <v>100.8871151336978</v>
       </c>
     </row>
     <row r="354" spans="1:5">
@@ -6398,13 +6398,13 @@
         <v>0</v>
       </c>
       <c r="C354">
-        <v>10.1</v>
+        <v>40.2</v>
       </c>
       <c r="D354">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="E354">
-        <v>30.3</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="355" spans="1:5">
@@ -6415,13 +6415,13 @@
         <v>0</v>
       </c>
       <c r="C355">
-        <v>20</v>
+        <v>260.5</v>
       </c>
       <c r="D355">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="E355">
-        <v>40</v>
+        <v>408.3141560122549</v>
       </c>
     </row>
     <row r="356" spans="1:5">
@@ -6432,13 +6432,13 @@
         <v>0</v>
       </c>
       <c r="C356">
-        <v>110.2</v>
+        <v>830.8</v>
       </c>
       <c r="D356">
-        <v>1001</v>
+        <v>6804</v>
       </c>
       <c r="E356">
-        <v>298.456294957905</v>
+        <v>2013.100484327595</v>
       </c>
     </row>
     <row r="357" spans="1:5">
@@ -6449,13 +6449,13 @@
         <v>0</v>
       </c>
       <c r="C357">
-        <v>20.1</v>
+        <v>50.3</v>
       </c>
       <c r="D357">
         <v>201</v>
       </c>
       <c r="E357">
-        <v>60.3</v>
+        <v>67.45524442176456</v>
       </c>
     </row>
     <row r="358" spans="1:5">
@@ -6466,13 +6466,13 @@
         <v>0</v>
       </c>
       <c r="C358">
-        <v>120.2</v>
+        <v>30.2</v>
       </c>
       <c r="D358">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="E358">
-        <v>299.6533997804797</v>
+        <v>64.40621088062858</v>
       </c>
     </row>
     <row r="359" spans="1:5">
@@ -6483,13 +6483,13 @@
         <v>0</v>
       </c>
       <c r="C359">
-        <v>0</v>
+        <v>110.2</v>
       </c>
       <c r="D359">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="E359">
-        <v>0</v>
+        <v>298.456294957905</v>
       </c>
     </row>
     <row r="360" spans="1:5">
@@ -6500,13 +6500,13 @@
         <v>0</v>
       </c>
       <c r="C360">
-        <v>20.1</v>
+        <v>10</v>
       </c>
       <c r="D360">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E360">
-        <v>40.20062188573704</v>
+        <v>30</v>
       </c>
     </row>
     <row r="361" spans="1:5">
@@ -6517,13 +6517,13 @@
         <v>0</v>
       </c>
       <c r="C361">
-        <v>66911910.4</v>
+        <v>72354156.2</v>
       </c>
       <c r="D361">
-        <v>178166101</v>
+        <v>103400565</v>
       </c>
       <c r="E361">
-        <v>48543094.7336027</v>
+        <v>37542499.46589301</v>
       </c>
     </row>
     <row r="362" spans="1:5">
@@ -6534,13 +6534,13 @@
         <v>0</v>
       </c>
       <c r="C362">
-        <v>12711264.5</v>
+        <v>37380088.8</v>
       </c>
       <c r="D362">
-        <v>60865738</v>
+        <v>96508307</v>
       </c>
       <c r="E362">
-        <v>17547898.92389934</v>
+        <v>35747833.40118018</v>
       </c>
     </row>
     <row r="363" spans="1:5">
@@ -6551,13 +6551,13 @@
         <v>0</v>
       </c>
       <c r="C363">
-        <v>2337069.5</v>
+        <v>12831404.3</v>
       </c>
       <c r="D363">
-        <v>15718912</v>
+        <v>35566423</v>
       </c>
       <c r="E363">
-        <v>4851640.774485004</v>
+        <v>13744487.69878859</v>
       </c>
     </row>
     <row r="364" spans="1:5">
@@ -6568,13 +6568,13 @@
         <v>0</v>
       </c>
       <c r="C364">
-        <v>1100.3</v>
+        <v>40.2</v>
       </c>
       <c r="D364">
-        <v>4900</v>
+        <v>201</v>
       </c>
       <c r="E364">
-        <v>1922.399648876372</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="365" spans="1:5">
@@ -6585,13 +6585,13 @@
         <v>0</v>
       </c>
       <c r="C365">
-        <v>110.1</v>
+        <v>150.3</v>
       </c>
       <c r="D365">
-        <v>1001</v>
+        <v>1101</v>
       </c>
       <c r="E365">
-        <v>298.4595282446181</v>
+        <v>326.6652874120542</v>
       </c>
     </row>
     <row r="366" spans="1:5">
@@ -6602,13 +6602,13 @@
         <v>0</v>
       </c>
       <c r="C366">
-        <v>20.1</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D366">
-        <v>201</v>
+        <v>901</v>
       </c>
       <c r="E366">
-        <v>60.3</v>
+        <v>270.3</v>
       </c>
     </row>
     <row r="367" spans="1:5">
@@ -6619,13 +6619,13 @@
         <v>0</v>
       </c>
       <c r="C367">
-        <v>10</v>
+        <v>40.2</v>
       </c>
       <c r="D367">
-        <v>100</v>
+        <v>201</v>
       </c>
       <c r="E367">
-        <v>30</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="368" spans="1:5">
@@ -6636,13 +6636,13 @@
         <v>0</v>
       </c>
       <c r="C368">
-        <v>20.1</v>
+        <v>100.1</v>
       </c>
       <c r="D368">
-        <v>201</v>
+        <v>1001</v>
       </c>
       <c r="E368">
-        <v>60.3</v>
+        <v>300.3</v>
       </c>
     </row>
     <row r="369" spans="1:5">
@@ -6653,13 +6653,13 @@
         <v>0</v>
       </c>
       <c r="C369">
-        <v>700.5</v>
+        <v>10.1</v>
       </c>
       <c r="D369">
-        <v>6804</v>
+        <v>101</v>
       </c>
       <c r="E369">
-        <v>2035.382384221697</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="370" spans="1:5">
@@ -6670,13 +6670,13 @@
         <v>0</v>
       </c>
       <c r="C370">
-        <v>40.2</v>
+        <v>30.2</v>
       </c>
       <c r="D370">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E370">
-        <v>80.40000000000001</v>
+        <v>64.5628376080234</v>
       </c>
     </row>
     <row r="371" spans="1:5">
@@ -6687,13 +6687,13 @@
         <v>0</v>
       </c>
       <c r="C371">
-        <v>30.2</v>
+        <v>20.1</v>
       </c>
       <c r="D371">
         <v>201</v>
       </c>
       <c r="E371">
-        <v>64.40621088062859</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="372" spans="1:5">
@@ -6704,13 +6704,13 @@
         <v>0</v>
       </c>
       <c r="C372">
-        <v>20.1</v>
+        <v>0</v>
       </c>
       <c r="D372">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="E372">
-        <v>40.20062188573704</v>
+        <v>0</v>
       </c>
     </row>
     <row r="373" spans="1:5">
@@ -6721,13 +6721,13 @@
         <v>0</v>
       </c>
       <c r="C373">
-        <v>90.40000000000001</v>
+        <v>150.4</v>
       </c>
       <c r="D373">
-        <v>201</v>
+        <v>901</v>
       </c>
       <c r="E373">
-        <v>94.80632890266347</v>
+        <v>280.6429047740206</v>
       </c>
     </row>
     <row r="374" spans="1:5">
@@ -6738,13 +6738,13 @@
         <v>0</v>
       </c>
       <c r="C374">
-        <v>10</v>
+        <v>140.3</v>
       </c>
       <c r="D374">
-        <v>100</v>
+        <v>1001</v>
       </c>
       <c r="E374">
-        <v>30</v>
+        <v>297.6511548776521</v>
       </c>
     </row>
     <row r="375" spans="1:5">
@@ -6755,13 +6755,13 @@
         <v>0</v>
       </c>
       <c r="C375">
-        <v>40.3</v>
+        <v>30.1</v>
       </c>
       <c r="D375">
-        <v>302</v>
+        <v>201</v>
       </c>
       <c r="E375">
-        <v>92.28439738113913</v>
+        <v>64.29688950485863</v>
       </c>
     </row>
     <row r="376" spans="1:5">
@@ -6775,10 +6775,10 @@
         <v>30.2</v>
       </c>
       <c r="D376">
-        <v>302</v>
+        <v>201</v>
       </c>
       <c r="E376">
-        <v>90.59999999999999</v>
+        <v>64.40621088062858</v>
       </c>
     </row>
     <row r="377" spans="1:5">
@@ -6789,13 +6789,13 @@
         <v>0</v>
       </c>
       <c r="C377">
-        <v>0</v>
+        <v>20.1</v>
       </c>
       <c r="D377">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="E377">
-        <v>0</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="378" spans="1:5">
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="C378">
-        <v>230.4</v>
+        <v>10.1</v>
       </c>
       <c r="D378">
-        <v>1102</v>
+        <v>101</v>
       </c>
       <c r="E378">
-        <v>413.0090071657033</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="379" spans="1:5">
@@ -6823,13 +6823,13 @@
         <v>0</v>
       </c>
       <c r="C379">
-        <v>90.5</v>
+        <v>10.1</v>
       </c>
       <c r="D379">
-        <v>402</v>
+        <v>101</v>
       </c>
       <c r="E379">
-        <v>130.7312127993923</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="380" spans="1:5">
@@ -6840,13 +6840,13 @@
         <v>0</v>
       </c>
       <c r="C380">
-        <v>30.1</v>
+        <v>50.2</v>
       </c>
       <c r="D380">
-        <v>201</v>
+        <v>301</v>
       </c>
       <c r="E380">
-        <v>64.29688950485863</v>
+        <v>102.8599047248246</v>
       </c>
     </row>
     <row r="381" spans="1:5">
@@ -6857,13 +6857,13 @@
         <v>0</v>
       </c>
       <c r="C381">
-        <v>87116708</v>
+        <v>77425599.90000001</v>
       </c>
       <c r="D381">
-        <v>163970707</v>
+        <v>148311847</v>
       </c>
       <c r="E381">
-        <v>49568189.66066749</v>
+        <v>47814005.39052006</v>
       </c>
     </row>
     <row r="382" spans="1:5">
@@ -6874,13 +6874,13 @@
         <v>0</v>
       </c>
       <c r="C382">
-        <v>55991778.4</v>
+        <v>34659835.3</v>
       </c>
       <c r="D382">
-        <v>125972999</v>
+        <v>85001055</v>
       </c>
       <c r="E382">
-        <v>41983174.52110359</v>
+        <v>31212263.68906093</v>
       </c>
     </row>
     <row r="383" spans="1:5">
@@ -6891,13 +6891,13 @@
         <v>0</v>
       </c>
       <c r="C383">
-        <v>15392223.4</v>
+        <v>11881461.5</v>
       </c>
       <c r="D383">
-        <v>54725041</v>
+        <v>59236133</v>
       </c>
       <c r="E383">
-        <v>20845592.55851879</v>
+        <v>23077766.4975748</v>
       </c>
     </row>
     <row r="384" spans="1:5">
@@ -6908,13 +6908,13 @@
         <v>0</v>
       </c>
       <c r="C384">
-        <v>160.5</v>
+        <v>40.2</v>
       </c>
       <c r="D384">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="E384">
-        <v>290.7924517589822</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="385" spans="1:5">
@@ -6925,13 +6925,13 @@
         <v>0</v>
       </c>
       <c r="C385">
-        <v>90.7</v>
+        <v>150.4</v>
       </c>
       <c r="D385">
-        <v>302</v>
+        <v>1001</v>
       </c>
       <c r="E385">
-        <v>94.94424679779181</v>
+        <v>294.4150811354609</v>
       </c>
     </row>
     <row r="386" spans="1:5">
@@ -6948,7 +6948,7 @@
         <v>1001</v>
       </c>
       <c r="E386">
-        <v>294.2248120060577</v>
+        <v>294.2591374961872</v>
       </c>
     </row>
     <row r="387" spans="1:5">
@@ -6959,13 +6959,13 @@
         <v>0</v>
       </c>
       <c r="C387">
-        <v>110.2</v>
+        <v>230.2</v>
       </c>
       <c r="D387">
-        <v>1102</v>
+        <v>1301</v>
       </c>
       <c r="E387">
-        <v>330.6</v>
+        <v>465.2613888987566</v>
       </c>
     </row>
     <row r="388" spans="1:5">
@@ -6976,13 +6976,13 @@
         <v>0</v>
       </c>
       <c r="C388">
-        <v>20.1</v>
+        <v>50.3</v>
       </c>
       <c r="D388">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="E388">
-        <v>40.20062188573705</v>
+        <v>81.05683191440434</v>
       </c>
     </row>
     <row r="389" spans="1:5">
@@ -6993,13 +6993,13 @@
         <v>0</v>
       </c>
       <c r="C389">
-        <v>80.5</v>
+        <v>30.1</v>
       </c>
       <c r="D389">
-        <v>302</v>
+        <v>201</v>
       </c>
       <c r="E389">
-        <v>125.7006364343475</v>
+        <v>64.29688950485863</v>
       </c>
     </row>
     <row r="390" spans="1:5">
@@ -7010,13 +7010,13 @@
         <v>0</v>
       </c>
       <c r="C390">
-        <v>80.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="D390">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="E390">
-        <v>98.46948765988377</v>
+        <v>0</v>
       </c>
     </row>
     <row r="391" spans="1:5">
@@ -7027,13 +7027,13 @@
         <v>0</v>
       </c>
       <c r="C391">
-        <v>20.1</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D391">
-        <v>201</v>
+        <v>301</v>
       </c>
       <c r="E391">
-        <v>60.3</v>
+        <v>114.0536715761487</v>
       </c>
     </row>
     <row r="392" spans="1:5">
@@ -7044,13 +7044,13 @@
         <v>0</v>
       </c>
       <c r="C392">
-        <v>120.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="D392">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="E392">
-        <v>299.6533997804797</v>
+        <v>90.46678948652925</v>
       </c>
     </row>
     <row r="393" spans="1:5">
@@ -7061,13 +7061,13 @@
         <v>0</v>
       </c>
       <c r="C393">
-        <v>10</v>
+        <v>170.4</v>
       </c>
       <c r="D393">
-        <v>100</v>
+        <v>1001</v>
       </c>
       <c r="E393">
-        <v>30</v>
+        <v>303.9151855370179</v>
       </c>
     </row>
     <row r="394" spans="1:5">
@@ -7078,13 +7078,13 @@
         <v>0</v>
       </c>
       <c r="C394">
-        <v>770.7</v>
+        <v>700.6</v>
       </c>
       <c r="D394">
-        <v>7405</v>
+        <v>6404</v>
       </c>
       <c r="E394">
-        <v>2212.348121340763</v>
+        <v>1902.724740996448</v>
       </c>
     </row>
     <row r="395" spans="1:5">
@@ -7095,13 +7095,13 @@
         <v>0</v>
       </c>
       <c r="C395">
-        <v>40.2</v>
+        <v>110.1</v>
       </c>
       <c r="D395">
-        <v>201</v>
+        <v>1001</v>
       </c>
       <c r="E395">
-        <v>80.40000000000001</v>
+        <v>298.4595282446181</v>
       </c>
     </row>
     <row r="396" spans="1:5">
@@ -7112,13 +7112,13 @@
         <v>0</v>
       </c>
       <c r="C396">
-        <v>130.3</v>
+        <v>100.1</v>
       </c>
       <c r="D396">
-        <v>1102</v>
+        <v>1001</v>
       </c>
       <c r="E396">
-        <v>329.397040059561</v>
+        <v>300.3</v>
       </c>
     </row>
     <row r="397" spans="1:5">
@@ -7129,13 +7129,13 @@
         <v>0</v>
       </c>
       <c r="C397">
-        <v>80.5</v>
+        <v>20.1</v>
       </c>
       <c r="D397">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="E397">
-        <v>87.63703555004585</v>
+        <v>40.20062188573705</v>
       </c>
     </row>
     <row r="398" spans="1:5">
@@ -7146,13 +7146,13 @@
         <v>0</v>
       </c>
       <c r="C398">
-        <v>220.4</v>
+        <v>20.1</v>
       </c>
       <c r="D398">
-        <v>1802</v>
+        <v>201</v>
       </c>
       <c r="E398">
-        <v>533.1270392692533</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="399" spans="1:5">
@@ -7163,13 +7163,13 @@
         <v>0</v>
       </c>
       <c r="C399">
-        <v>190.2</v>
+        <v>60.3</v>
       </c>
       <c r="D399">
-        <v>1001</v>
+        <v>402</v>
       </c>
       <c r="E399">
-        <v>381.0566362104195</v>
+        <v>128.7027971724002</v>
       </c>
     </row>
     <row r="400" spans="1:5">
@@ -7180,13 +7180,13 @@
         <v>0</v>
       </c>
       <c r="C400">
-        <v>200.2</v>
+        <v>120.1</v>
       </c>
       <c r="D400">
-        <v>1001</v>
+        <v>1101</v>
       </c>
       <c r="E400">
-        <v>377.2269343511939</v>
+        <v>328.323148742211</v>
       </c>
     </row>
     <row r="401" spans="1:5">
@@ -7197,13 +7197,13 @@
         <v>0</v>
       </c>
       <c r="C401">
-        <v>78140006</v>
+        <v>52383441.7</v>
       </c>
       <c r="D401">
-        <v>175146351</v>
+        <v>113869596</v>
       </c>
       <c r="E401">
-        <v>52340897.2102674</v>
+        <v>33844030.29024692</v>
       </c>
     </row>
     <row r="402" spans="1:5">
@@ -7214,13 +7214,13 @@
         <v>0</v>
       </c>
       <c r="C402">
-        <v>17460507.2</v>
+        <v>27665730.2</v>
       </c>
       <c r="D402">
-        <v>62618914</v>
+        <v>65607158</v>
       </c>
       <c r="E402">
-        <v>23691039.47181911</v>
+        <v>23196832.08731211</v>
       </c>
     </row>
     <row r="403" spans="1:5">
@@ -7231,13 +7231,13 @@
         <v>0</v>
       </c>
       <c r="C403">
-        <v>134365.8</v>
+        <v>8592066.1</v>
       </c>
       <c r="D403">
-        <v>757485</v>
+        <v>38995776</v>
       </c>
       <c r="E403">
-        <v>225223.4210115813</v>
+        <v>12059259.13085905</v>
       </c>
     </row>
     <row r="404" spans="1:5">
@@ -7248,13 +7248,13 @@
         <v>0</v>
       </c>
       <c r="C404">
-        <v>80.40000000000001</v>
+        <v>1744837.4</v>
       </c>
       <c r="D404">
-        <v>302</v>
+        <v>16004961</v>
       </c>
       <c r="E404">
-        <v>108.3348512714168</v>
+        <v>4772790.818542317</v>
       </c>
     </row>
     <row r="405" spans="1:5">
@@ -7265,13 +7265,13 @@
         <v>0</v>
       </c>
       <c r="C405">
-        <v>140.4</v>
+        <v>50.4</v>
       </c>
       <c r="D405">
-        <v>901</v>
+        <v>202</v>
       </c>
       <c r="E405">
-        <v>265.6468332203492</v>
+        <v>81.2430920140291</v>
       </c>
     </row>
     <row r="406" spans="1:5">
@@ -7282,13 +7282,13 @@
         <v>0</v>
       </c>
       <c r="C406">
-        <v>10.1</v>
+        <v>100.1</v>
       </c>
       <c r="D406">
-        <v>101</v>
+        <v>1001</v>
       </c>
       <c r="E406">
-        <v>30.3</v>
+        <v>300.3</v>
       </c>
     </row>
     <row r="407" spans="1:5">
@@ -7299,13 +7299,13 @@
         <v>0</v>
       </c>
       <c r="C407">
-        <v>20.1</v>
+        <v>130.2</v>
       </c>
       <c r="D407">
-        <v>201</v>
+        <v>1001</v>
       </c>
       <c r="E407">
-        <v>60.3</v>
+        <v>297.133236107979</v>
       </c>
     </row>
     <row r="408" spans="1:5">
@@ -7316,13 +7316,13 @@
         <v>0</v>
       </c>
       <c r="C408">
-        <v>50.3</v>
+        <v>10</v>
       </c>
       <c r="D408">
-        <v>201</v>
+        <v>100</v>
       </c>
       <c r="E408">
-        <v>81.05683191440434</v>
+        <v>30</v>
       </c>
     </row>
     <row r="409" spans="1:5">
@@ -7333,13 +7333,13 @@
         <v>0</v>
       </c>
       <c r="C409">
-        <v>20.1</v>
+        <v>30.2</v>
       </c>
       <c r="D409">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="E409">
-        <v>40.20062188573705</v>
+        <v>64.40621088062859</v>
       </c>
     </row>
     <row r="410" spans="1:5">
@@ -7350,13 +7350,13 @@
         <v>0</v>
       </c>
       <c r="C410">
-        <v>40.2</v>
+        <v>50.1</v>
       </c>
       <c r="D410">
         <v>201</v>
       </c>
       <c r="E410">
-        <v>80.40000000000001</v>
+        <v>67.30594327397841</v>
       </c>
     </row>
     <row r="411" spans="1:5">
@@ -7367,13 +7367,13 @@
         <v>0</v>
       </c>
       <c r="C411">
-        <v>30.3</v>
+        <v>40.2</v>
       </c>
       <c r="D411">
-        <v>102</v>
+        <v>201</v>
       </c>
       <c r="E411">
-        <v>46.28617504179839</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="412" spans="1:5">
@@ -7384,13 +7384,13 @@
         <v>0</v>
       </c>
       <c r="C412">
-        <v>140.4</v>
+        <v>50.2</v>
       </c>
       <c r="D412">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="E412">
-        <v>297.6716983523963</v>
+        <v>80.99481464884033</v>
       </c>
     </row>
     <row r="413" spans="1:5">
@@ -7401,13 +7401,13 @@
         <v>0</v>
       </c>
       <c r="C413">
-        <v>20.1</v>
+        <v>120.2</v>
       </c>
       <c r="D413">
-        <v>201</v>
+        <v>1202</v>
       </c>
       <c r="E413">
-        <v>60.3</v>
+        <v>360.6</v>
       </c>
     </row>
     <row r="414" spans="1:5">
@@ -7418,13 +7418,13 @@
         <v>0</v>
       </c>
       <c r="C414">
-        <v>30.2</v>
+        <v>140.2</v>
       </c>
       <c r="D414">
-        <v>201</v>
+        <v>1101</v>
       </c>
       <c r="E414">
-        <v>64.40621088062859</v>
+        <v>326.5029249486136</v>
       </c>
     </row>
     <row r="415" spans="1:5">
@@ -7435,13 +7435,13 @@
         <v>0</v>
       </c>
       <c r="C415">
-        <v>120.2</v>
+        <v>40.1</v>
       </c>
       <c r="D415">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="E415">
-        <v>299.6533997804797</v>
+        <v>66.57394385193055</v>
       </c>
     </row>
     <row r="416" spans="1:5">
@@ -7452,13 +7452,13 @@
         <v>0</v>
       </c>
       <c r="C416">
-        <v>30.1</v>
+        <v>50.2</v>
       </c>
       <c r="D416">
         <v>201</v>
       </c>
       <c r="E416">
-        <v>64.29688950485864</v>
+        <v>80.99481464884033</v>
       </c>
     </row>
     <row r="417" spans="1:5">
@@ -7469,13 +7469,13 @@
         <v>0</v>
       </c>
       <c r="C417">
-        <v>10</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="D417">
-        <v>100</v>
+        <v>302</v>
       </c>
       <c r="E417">
-        <v>30</v>
+        <v>108.3348512714168</v>
       </c>
     </row>
     <row r="418" spans="1:5">
@@ -7486,13 +7486,13 @@
         <v>0</v>
       </c>
       <c r="C418">
-        <v>20.1</v>
+        <v>10</v>
       </c>
       <c r="D418">
-        <v>201</v>
+        <v>100</v>
       </c>
       <c r="E418">
-        <v>60.3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="419" spans="1:5">
@@ -7503,13 +7503,13 @@
         <v>0</v>
       </c>
       <c r="C419">
-        <v>40.3</v>
+        <v>10</v>
       </c>
       <c r="D419">
-        <v>201</v>
+        <v>100</v>
       </c>
       <c r="E419">
-        <v>66.75485001106661</v>
+        <v>30</v>
       </c>
     </row>
     <row r="420" spans="1:5">
@@ -7520,13 +7520,13 @@
         <v>0</v>
       </c>
       <c r="C420">
-        <v>100.1</v>
+        <v>70.3</v>
       </c>
       <c r="D420">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="E420">
-        <v>300.3</v>
+        <v>90.43345619846671</v>
       </c>
     </row>
     <row r="421" spans="1:5">
@@ -7537,13 +7537,13 @@
         <v>0</v>
       </c>
       <c r="C421">
-        <v>80340648.59999999</v>
+        <v>59014496.3</v>
       </c>
       <c r="D421">
-        <v>200296873</v>
+        <v>116213538</v>
       </c>
       <c r="E421">
-        <v>67312943.11998847</v>
+        <v>37375420.94431573</v>
       </c>
     </row>
     <row r="422" spans="1:5">
@@ -7554,13 +7554,13 @@
         <v>0</v>
       </c>
       <c r="C422">
-        <v>28736479.9</v>
+        <v>22405793.2</v>
       </c>
       <c r="D422">
-        <v>108547902</v>
+        <v>83573934</v>
       </c>
       <c r="E422">
-        <v>33477411.36975909</v>
+        <v>27196628.13613925</v>
       </c>
     </row>
     <row r="423" spans="1:5">
@@ -7571,13 +7571,13 @@
         <v>0</v>
       </c>
       <c r="C423">
-        <v>3293661</v>
+        <v>238251</v>
       </c>
       <c r="D423">
-        <v>17751513</v>
+        <v>731589</v>
       </c>
       <c r="E423">
-        <v>5474674.21620465</v>
+        <v>309150.1111816071</v>
       </c>
     </row>
     <row r="424" spans="1:5">
@@ -7588,13 +7588,13 @@
         <v>0</v>
       </c>
       <c r="C424">
-        <v>832106.1</v>
+        <v>230.5</v>
       </c>
       <c r="D424">
-        <v>8320256</v>
+        <v>901</v>
       </c>
       <c r="E424">
-        <v>2496049.969679552</v>
+        <v>293.8200980191791</v>
       </c>
     </row>
     <row r="425" spans="1:5">
@@ -7605,13 +7605,13 @@
         <v>0</v>
       </c>
       <c r="C425">
-        <v>0</v>
+        <v>150.4</v>
       </c>
       <c r="D425">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="E425">
-        <v>0</v>
+        <v>301.198339968865</v>
       </c>
     </row>
     <row r="426" spans="1:5">
@@ -7622,13 +7622,13 @@
         <v>0</v>
       </c>
       <c r="C426">
-        <v>170.3</v>
+        <v>130.2</v>
       </c>
       <c r="D426">
-        <v>1402</v>
+        <v>901</v>
       </c>
       <c r="E426">
-        <v>420.2599314709886</v>
+        <v>265.081421453862</v>
       </c>
     </row>
     <row r="427" spans="1:5">
@@ -7639,13 +7639,13 @@
         <v>0</v>
       </c>
       <c r="C427">
-        <v>20.1</v>
+        <v>850.6</v>
       </c>
       <c r="D427">
-        <v>201</v>
+        <v>6804</v>
       </c>
       <c r="E427">
-        <v>60.3</v>
+        <v>2048.316782140887</v>
       </c>
     </row>
     <row r="428" spans="1:5">
@@ -7656,13 +7656,13 @@
         <v>0</v>
       </c>
       <c r="C428">
-        <v>30.1</v>
+        <v>40.2</v>
       </c>
       <c r="D428">
-        <v>301</v>
+        <v>201</v>
       </c>
       <c r="E428">
-        <v>90.29999999999998</v>
+        <v>66.66453329919891</v>
       </c>
     </row>
     <row r="429" spans="1:5">
@@ -7673,13 +7673,13 @@
         <v>0</v>
       </c>
       <c r="C429">
-        <v>30.1</v>
+        <v>130.1</v>
       </c>
       <c r="D429">
-        <v>201</v>
+        <v>1001</v>
       </c>
       <c r="E429">
-        <v>64.29688950485863</v>
+        <v>293.7245137880051</v>
       </c>
     </row>
     <row r="430" spans="1:5">
@@ -7690,13 +7690,13 @@
         <v>0</v>
       </c>
       <c r="C430">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="D430">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="E430">
-        <v>64.40621088062859</v>
+        <v>45.9792344433876</v>
       </c>
     </row>
     <row r="431" spans="1:5">
@@ -7707,13 +7707,13 @@
         <v>0</v>
       </c>
       <c r="C431">
-        <v>20.2</v>
+        <v>40.2</v>
       </c>
       <c r="D431">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="E431">
-        <v>40.4</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="432" spans="1:5">
@@ -7724,13 +7724,13 @@
         <v>0</v>
       </c>
       <c r="C432">
-        <v>20.1</v>
+        <v>40.2</v>
       </c>
       <c r="D432">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="E432">
-        <v>40.20062188573704</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="433" spans="1:5">
@@ -7741,13 +7741,13 @@
         <v>0</v>
       </c>
       <c r="C433">
-        <v>0</v>
+        <v>30.1</v>
       </c>
       <c r="D433">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="E433">
-        <v>0</v>
+        <v>64.29688950485863</v>
       </c>
     </row>
     <row r="434" spans="1:5">
@@ -7758,13 +7758,13 @@
         <v>0</v>
       </c>
       <c r="C434">
-        <v>20.1</v>
+        <v>0</v>
       </c>
       <c r="D434">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="E434">
-        <v>60.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="435" spans="1:5">
@@ -7775,13 +7775,13 @@
         <v>0</v>
       </c>
       <c r="C435">
-        <v>20.2</v>
+        <v>840.6</v>
       </c>
       <c r="D435">
-        <v>101</v>
+        <v>6404</v>
       </c>
       <c r="E435">
-        <v>40.4</v>
+        <v>1921.695459743817</v>
       </c>
     </row>
     <row r="436" spans="1:5">
@@ -7792,13 +7792,13 @@
         <v>0</v>
       </c>
       <c r="C436">
-        <v>50.2</v>
+        <v>130.2</v>
       </c>
       <c r="D436">
-        <v>402</v>
+        <v>1001</v>
       </c>
       <c r="E436">
-        <v>120.9973553429991</v>
+        <v>297.133236107979</v>
       </c>
     </row>
     <row r="437" spans="1:5">
@@ -7809,13 +7809,13 @@
         <v>0</v>
       </c>
       <c r="C437">
-        <v>30.1</v>
+        <v>120.2</v>
       </c>
       <c r="D437">
-        <v>201</v>
+        <v>901</v>
       </c>
       <c r="E437">
-        <v>64.29688950485864</v>
+        <v>267.903266124174</v>
       </c>
     </row>
     <row r="438" spans="1:5">
@@ -7826,13 +7826,13 @@
         <v>0</v>
       </c>
       <c r="C438">
-        <v>160.3</v>
+        <v>40.2</v>
       </c>
       <c r="D438">
-        <v>1303</v>
+        <v>201</v>
       </c>
       <c r="E438">
-        <v>383.5163751393153</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="439" spans="1:5">
@@ -7843,13 +7843,13 @@
         <v>0</v>
       </c>
       <c r="C439">
-        <v>1290.8</v>
+        <v>50.3</v>
       </c>
       <c r="D439">
-        <v>6504</v>
+        <v>201</v>
       </c>
       <c r="E439">
-        <v>2581.696837353294</v>
+        <v>81.05683191440434</v>
       </c>
     </row>
     <row r="440" spans="1:5">
@@ -7860,13 +7860,13 @@
         <v>0</v>
       </c>
       <c r="C440">
-        <v>10.1</v>
+        <v>20.1</v>
       </c>
       <c r="D440">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="E440">
-        <v>30.3</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="441" spans="1:5">
@@ -7877,13 +7877,13 @@
         <v>0</v>
       </c>
       <c r="C441">
-        <v>65663717.6</v>
+        <v>92342983</v>
       </c>
       <c r="D441">
-        <v>155811434</v>
+        <v>189352651</v>
       </c>
       <c r="E441">
-        <v>54431496.02413537</v>
+        <v>59528770.42699328</v>
       </c>
     </row>
     <row r="442" spans="1:5">
@@ -7894,13 +7894,13 @@
         <v>0</v>
       </c>
       <c r="C442">
-        <v>6378604.4</v>
+        <v>32637701.8</v>
       </c>
       <c r="D442">
-        <v>40675499</v>
+        <v>126050574</v>
       </c>
       <c r="E442">
-        <v>12136538.5507983</v>
+        <v>39404926.14446229</v>
       </c>
     </row>
     <row r="443" spans="1:5">
@@ -7911,13 +7911,13 @@
         <v>0</v>
       </c>
       <c r="C443">
-        <v>115195</v>
+        <v>1061.1</v>
       </c>
       <c r="D443">
-        <v>1150849</v>
+        <v>7005</v>
       </c>
       <c r="E443">
-        <v>345218.1270663521</v>
+        <v>2040.605324407441</v>
       </c>
     </row>
     <row r="444" spans="1:5">
@@ -7928,13 +7928,13 @@
         <v>0</v>
       </c>
       <c r="C444">
-        <v>40.2</v>
+        <v>270.6</v>
       </c>
       <c r="D444">
-        <v>201</v>
+        <v>1001</v>
       </c>
       <c r="E444">
-        <v>80.40000000000001</v>
+        <v>385.222585007681</v>
       </c>
     </row>
     <row r="445" spans="1:5">
@@ -7945,13 +7945,13 @@
         <v>0</v>
       </c>
       <c r="C445">
-        <v>60.1</v>
+        <v>160.4</v>
       </c>
       <c r="D445">
-        <v>501</v>
+        <v>1001</v>
       </c>
       <c r="E445">
-        <v>149.9602947449758</v>
+        <v>307.688868826937</v>
       </c>
     </row>
     <row r="446" spans="1:5">
@@ -7962,13 +7962,13 @@
         <v>0</v>
       </c>
       <c r="C446">
-        <v>30.2</v>
+        <v>40.2</v>
       </c>
       <c r="D446">
         <v>201</v>
       </c>
       <c r="E446">
-        <v>64.40621088062858</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="447" spans="1:5">
@@ -7979,13 +7979,13 @@
         <v>0</v>
       </c>
       <c r="C447">
-        <v>220.6</v>
+        <v>330.7</v>
       </c>
       <c r="D447">
-        <v>1702</v>
+        <v>1001</v>
       </c>
       <c r="E447">
-        <v>498.1130795311442</v>
+        <v>440.8160727559738</v>
       </c>
     </row>
     <row r="448" spans="1:5">
@@ -7996,13 +7996,13 @@
         <v>0</v>
       </c>
       <c r="C448">
-        <v>100.1</v>
+        <v>120.2</v>
       </c>
       <c r="D448">
         <v>1001</v>
       </c>
       <c r="E448">
-        <v>300.3</v>
+        <v>299.6533997804797</v>
       </c>
     </row>
     <row r="449" spans="1:5">
@@ -8013,13 +8013,13 @@
         <v>0</v>
       </c>
       <c r="C449">
-        <v>120.2</v>
+        <v>40.2</v>
       </c>
       <c r="D449">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="E449">
-        <v>299.6533997804797</v>
+        <v>66.66453329919891</v>
       </c>
     </row>
     <row r="450" spans="1:5">
@@ -8030,13 +8030,13 @@
         <v>0</v>
       </c>
       <c r="C450">
-        <v>0</v>
+        <v>140.2</v>
       </c>
       <c r="D450">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="E450">
-        <v>0</v>
+        <v>294.2518649048804</v>
       </c>
     </row>
     <row r="451" spans="1:5">
@@ -8047,13 +8047,13 @@
         <v>0</v>
       </c>
       <c r="C451">
-        <v>30.2</v>
+        <v>40.2</v>
       </c>
       <c r="D451">
         <v>201</v>
       </c>
       <c r="E451">
-        <v>64.40621088062859</v>
+        <v>66.66453329919891</v>
       </c>
     </row>
     <row r="452" spans="1:5">
@@ -8064,13 +8064,13 @@
         <v>0</v>
       </c>
       <c r="C452">
-        <v>60.3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="D452">
-        <v>201</v>
+        <v>402</v>
       </c>
       <c r="E452">
-        <v>92.10977146861238</v>
+        <v>160.8</v>
       </c>
     </row>
     <row r="453" spans="1:5">
@@ -8081,13 +8081,13 @@
         <v>0</v>
       </c>
       <c r="C453">
-        <v>40.2</v>
+        <v>30.1</v>
       </c>
       <c r="D453">
         <v>201</v>
       </c>
       <c r="E453">
-        <v>80.40000000000001</v>
+        <v>64.29688950485864</v>
       </c>
     </row>
     <row r="454" spans="1:5">
@@ -8098,13 +8098,13 @@
         <v>0</v>
       </c>
       <c r="C454">
-        <v>70.3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="D454">
         <v>201</v>
       </c>
       <c r="E454">
-        <v>90.43345619846671</v>
+        <v>87.61415410765547</v>
       </c>
     </row>
     <row r="455" spans="1:5">
@@ -8115,13 +8115,13 @@
         <v>0</v>
       </c>
       <c r="C455">
-        <v>760.6</v>
+        <v>150.4</v>
       </c>
       <c r="D455">
-        <v>7405</v>
+        <v>1102</v>
       </c>
       <c r="E455">
-        <v>2215.610579501732</v>
+        <v>326.9563273588691</v>
       </c>
     </row>
     <row r="456" spans="1:5">
@@ -8132,13 +8132,13 @@
         <v>0</v>
       </c>
       <c r="C456">
-        <v>230.2</v>
+        <v>20.1</v>
       </c>
       <c r="D456">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="E456">
-        <v>379.9844207332716</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="457" spans="1:5">
@@ -8149,13 +8149,13 @@
         <v>0</v>
       </c>
       <c r="C457">
-        <v>0</v>
+        <v>20.1</v>
       </c>
       <c r="D457">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="E457">
-        <v>0</v>
+        <v>40.20062188573705</v>
       </c>
     </row>
     <row r="458" spans="1:5">
@@ -8166,13 +8166,13 @@
         <v>0</v>
       </c>
       <c r="C458">
-        <v>50.3</v>
+        <v>0</v>
       </c>
       <c r="D458">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="E458">
-        <v>81.05683191440434</v>
+        <v>0</v>
       </c>
     </row>
     <row r="459" spans="1:5">
@@ -8183,13 +8183,13 @@
         <v>0</v>
       </c>
       <c r="C459">
-        <v>30.2</v>
+        <v>140.2</v>
       </c>
       <c r="D459">
-        <v>302</v>
+        <v>1302</v>
       </c>
       <c r="E459">
-        <v>90.59999999999999</v>
+        <v>388.4126156550531</v>
       </c>
     </row>
     <row r="460" spans="1:5">
@@ -8200,13 +8200,13 @@
         <v>0</v>
       </c>
       <c r="C460">
-        <v>50.2</v>
+        <v>220.3</v>
       </c>
       <c r="D460">
-        <v>201</v>
+        <v>1001</v>
       </c>
       <c r="E460">
-        <v>67.38070940558582</v>
+        <v>371.3330176539652</v>
       </c>
     </row>
     <row r="461" spans="1:5">
@@ -8217,13 +8217,13 @@
         <v>0</v>
       </c>
       <c r="C461">
-        <v>65439759.5</v>
+        <v>84497001.90000001</v>
       </c>
       <c r="D461">
-        <v>205444316</v>
+        <v>235533113</v>
       </c>
       <c r="E461">
-        <v>55463392.66226098</v>
+        <v>66102769.01047406</v>
       </c>
     </row>
     <row r="462" spans="1:5">
@@ -8234,13 +8234,13 @@
         <v>0</v>
       </c>
       <c r="C462">
-        <v>18496799.3</v>
+        <v>31433714.4</v>
       </c>
       <c r="D462">
-        <v>66926677</v>
+        <v>82644646</v>
       </c>
       <c r="E462">
-        <v>23936117.06217449</v>
+        <v>28794226.53696684</v>
       </c>
     </row>
     <row r="463" spans="1:5">
@@ -8251,13 +8251,13 @@
         <v>0</v>
       </c>
       <c r="C463">
-        <v>2549619.5</v>
+        <v>12952460.2</v>
       </c>
       <c r="D463">
-        <v>23373441</v>
+        <v>54579015</v>
       </c>
       <c r="E463">
-        <v>6951072.080452184</v>
+        <v>16079666.17491114</v>
       </c>
     </row>
     <row r="464" spans="1:5">
@@ -8268,13 +8268,13 @@
         <v>0</v>
       </c>
       <c r="C464">
-        <v>2336264.5</v>
+        <v>3585075.8</v>
       </c>
       <c r="D464">
-        <v>23362243</v>
+        <v>19286268</v>
       </c>
       <c r="E464">
-        <v>7008659.500448345</v>
+        <v>6157715.380579177</v>
       </c>
     </row>
     <row r="465" spans="1:5">
@@ -8285,13 +8285,13 @@
         <v>0</v>
       </c>
       <c r="C465">
-        <v>100.1</v>
+        <v>112741.9</v>
       </c>
       <c r="D465">
-        <v>901</v>
+        <v>980281</v>
       </c>
       <c r="E465">
-        <v>268.6263017651101</v>
+        <v>290053.544527713</v>
       </c>
     </row>
     <row r="466" spans="1:5">
@@ -8302,13 +8302,13 @@
         <v>0</v>
       </c>
       <c r="C466">
-        <v>50.2</v>
+        <v>7721.3</v>
       </c>
       <c r="D466">
-        <v>301</v>
+        <v>76309</v>
       </c>
       <c r="E466">
-        <v>102.8599047248246</v>
+        <v>22862.83129470189</v>
       </c>
     </row>
     <row r="467" spans="1:5">
@@ -8319,13 +8319,13 @@
         <v>0</v>
       </c>
       <c r="C467">
-        <v>150.4</v>
+        <v>50.3</v>
       </c>
       <c r="D467">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="E467">
-        <v>294.4150811354609</v>
+        <v>81.05683191440434</v>
       </c>
     </row>
     <row r="468" spans="1:5">
@@ -8336,13 +8336,13 @@
         <v>0</v>
       </c>
       <c r="C468">
-        <v>30.2</v>
+        <v>20.2</v>
       </c>
       <c r="D468">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="E468">
-        <v>64.40621088062858</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="469" spans="1:5">
@@ -8353,13 +8353,13 @@
         <v>0</v>
       </c>
       <c r="C469">
-        <v>80.5</v>
+        <v>100.2</v>
       </c>
       <c r="D469">
-        <v>302</v>
+        <v>901</v>
       </c>
       <c r="E469">
-        <v>125.7006364343475</v>
+        <v>268.6264320576067</v>
       </c>
     </row>
     <row r="470" spans="1:5">
@@ -8370,13 +8370,13 @@
         <v>0</v>
       </c>
       <c r="C470">
-        <v>2471.3</v>
+        <v>120.2</v>
       </c>
       <c r="D470">
-        <v>23409</v>
+        <v>1001</v>
       </c>
       <c r="E470">
-        <v>6986.868054428965</v>
+        <v>299.6533997804797</v>
       </c>
     </row>
     <row r="471" spans="1:5">
@@ -8387,13 +8387,13 @@
         <v>0</v>
       </c>
       <c r="C471">
-        <v>210.2</v>
+        <v>170.5</v>
       </c>
       <c r="D471">
         <v>1001</v>
       </c>
       <c r="E471">
-        <v>396.5049306124704</v>
+        <v>290.3281763797651</v>
       </c>
     </row>
     <row r="472" spans="1:5">
@@ -8404,13 +8404,13 @@
         <v>0</v>
       </c>
       <c r="C472">
-        <v>50.2</v>
+        <v>40.2</v>
       </c>
       <c r="D472">
-        <v>301</v>
+        <v>201</v>
       </c>
       <c r="E472">
-        <v>102.8599047248246</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="473" spans="1:5">
@@ -8421,13 +8421,13 @@
         <v>0</v>
       </c>
       <c r="C473">
-        <v>0</v>
+        <v>50.3</v>
       </c>
       <c r="D473">
-        <v>0</v>
+        <v>302</v>
       </c>
       <c r="E473">
-        <v>0</v>
+        <v>92.79229493875016</v>
       </c>
     </row>
     <row r="474" spans="1:5">
@@ -8438,13 +8438,13 @@
         <v>0</v>
       </c>
       <c r="C474">
-        <v>10.1</v>
+        <v>110.1</v>
       </c>
       <c r="D474">
-        <v>101</v>
+        <v>1001</v>
       </c>
       <c r="E474">
-        <v>30.3</v>
+        <v>298.4595282446181</v>
       </c>
     </row>
     <row r="475" spans="1:5">
@@ -8455,13 +8455,13 @@
         <v>0</v>
       </c>
       <c r="C475">
-        <v>40.1</v>
+        <v>20</v>
       </c>
       <c r="D475">
-        <v>201</v>
+        <v>100</v>
       </c>
       <c r="E475">
-        <v>66.57394385193055</v>
+        <v>40</v>
       </c>
     </row>
     <row r="476" spans="1:5">
@@ -8472,13 +8472,13 @@
         <v>0</v>
       </c>
       <c r="C476">
-        <v>40.4</v>
+        <v>30.2</v>
       </c>
       <c r="D476">
-        <v>202</v>
+        <v>102</v>
       </c>
       <c r="E476">
-        <v>80.8</v>
+        <v>46.13415220853202</v>
       </c>
     </row>
     <row r="477" spans="1:5">
@@ -8489,13 +8489,13 @@
         <v>0</v>
       </c>
       <c r="C477">
-        <v>80.5</v>
+        <v>60.3</v>
       </c>
       <c r="D477">
-        <v>202</v>
+        <v>301</v>
       </c>
       <c r="E477">
-        <v>98.59234250183937</v>
+        <v>102.3924313609165</v>
       </c>
     </row>
     <row r="478" spans="1:5">
@@ -8506,13 +8506,13 @@
         <v>0</v>
       </c>
       <c r="C478">
-        <v>120.6</v>
+        <v>30.1</v>
       </c>
       <c r="D478">
         <v>201</v>
       </c>
       <c r="E478">
-        <v>87.61415410765547</v>
+        <v>64.29688950485864</v>
       </c>
     </row>
     <row r="479" spans="1:5">
@@ -8523,13 +8523,13 @@
         <v>0</v>
       </c>
       <c r="C479">
-        <v>70.3</v>
+        <v>30.1</v>
       </c>
       <c r="D479">
-        <v>301</v>
+        <v>201</v>
       </c>
       <c r="E479">
-        <v>100.8871151336978</v>
+        <v>64.29688950485864</v>
       </c>
     </row>
     <row r="480" spans="1:5">
@@ -8540,13 +8540,13 @@
         <v>0</v>
       </c>
       <c r="C480">
-        <v>90.09999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="D480">
-        <v>901</v>
+        <v>402</v>
       </c>
       <c r="E480">
-        <v>270.3</v>
+        <v>130.6623128526355</v>
       </c>
     </row>
     <row r="481" spans="1:5">
@@ -8557,13 +8557,13 @@
         <v>0</v>
       </c>
       <c r="C481">
-        <v>106033451.7</v>
+        <v>31819548.5</v>
       </c>
       <c r="D481">
-        <v>230187483</v>
+        <v>120261692</v>
       </c>
       <c r="E481">
-        <v>66323905.78304436</v>
+        <v>41037862.51010311</v>
       </c>
     </row>
     <row r="482" spans="1:5">
@@ -8574,13 +8574,13 @@
         <v>0</v>
       </c>
       <c r="C482">
-        <v>47587763.8</v>
+        <v>9611237</v>
       </c>
       <c r="D482">
-        <v>88254798</v>
+        <v>37244831</v>
       </c>
       <c r="E482">
-        <v>31332305.98217815</v>
+        <v>13295082.58147671</v>
       </c>
     </row>
     <row r="483" spans="1:5">
@@ -8591,13 +8591,13 @@
         <v>0</v>
       </c>
       <c r="C483">
-        <v>14700343.6</v>
+        <v>719289.7</v>
       </c>
       <c r="D483">
-        <v>29691778</v>
+        <v>3454809</v>
       </c>
       <c r="E483">
-        <v>8795974.035415135</v>
+        <v>1133856.661654995</v>
       </c>
     </row>
     <row r="484" spans="1:5">
@@ -8608,13 +8608,13 @@
         <v>0</v>
       </c>
       <c r="C484">
-        <v>9407238.6</v>
+        <v>15430.8</v>
       </c>
       <c r="D484">
-        <v>19333512</v>
+        <v>49401</v>
       </c>
       <c r="E484">
-        <v>7707094.691025396</v>
+        <v>22113.57307537613</v>
       </c>
     </row>
     <row r="485" spans="1:5">
@@ -8625,13 +8625,13 @@
         <v>0</v>
       </c>
       <c r="C485">
-        <v>3227853.5</v>
+        <v>791</v>
       </c>
       <c r="D485">
-        <v>12983733</v>
+        <v>6804</v>
       </c>
       <c r="E485">
-        <v>4457479.635888362</v>
+        <v>2007.247219452552</v>
       </c>
     </row>
     <row r="486" spans="1:5">
@@ -8642,13 +8642,13 @@
         <v>0</v>
       </c>
       <c r="C486">
-        <v>5012</v>
+        <v>280.6</v>
       </c>
       <c r="D486">
-        <v>26610</v>
+        <v>1101</v>
       </c>
       <c r="E486">
-        <v>10024.38098837031</v>
+        <v>399.8555239083237</v>
       </c>
     </row>
     <row r="487" spans="1:5">
@@ -8659,13 +8659,13 @@
         <v>0</v>
       </c>
       <c r="C487">
-        <v>190.4</v>
+        <v>40.3</v>
       </c>
       <c r="D487">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="E487">
-        <v>298.4433614607636</v>
+        <v>66.75485001106661</v>
       </c>
     </row>
     <row r="488" spans="1:5">
@@ -8676,13 +8676,13 @@
         <v>0</v>
       </c>
       <c r="C488">
-        <v>290.5</v>
+        <v>200.4</v>
       </c>
       <c r="D488">
-        <v>1001</v>
+        <v>1802</v>
       </c>
       <c r="E488">
-        <v>353.70927327397</v>
+        <v>535.3509503120359</v>
       </c>
     </row>
     <row r="489" spans="1:5">
@@ -8693,13 +8693,13 @@
         <v>0</v>
       </c>
       <c r="C489">
-        <v>80.40000000000001</v>
+        <v>150.5</v>
       </c>
       <c r="D489">
-        <v>202</v>
+        <v>901</v>
       </c>
       <c r="E489">
-        <v>87.72935654614139</v>
+        <v>262.050472237697</v>
       </c>
     </row>
     <row r="490" spans="1:5">
@@ -8710,13 +8710,13 @@
         <v>0</v>
       </c>
       <c r="C490">
-        <v>20.1</v>
+        <v>120.2</v>
       </c>
       <c r="D490">
-        <v>101</v>
+        <v>901</v>
       </c>
       <c r="E490">
-        <v>40.20062188573705</v>
+        <v>267.903266124174</v>
       </c>
     </row>
     <row r="491" spans="1:5">
@@ -8727,13 +8727,13 @@
         <v>0</v>
       </c>
       <c r="C491">
-        <v>60.3</v>
+        <v>0</v>
       </c>
       <c r="D491">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="E491">
-        <v>92.10977146861238</v>
+        <v>0</v>
       </c>
     </row>
     <row r="492" spans="1:5">
@@ -8744,13 +8744,13 @@
         <v>0</v>
       </c>
       <c r="C492">
-        <v>40.2</v>
+        <v>50.2</v>
       </c>
       <c r="D492">
         <v>201</v>
       </c>
       <c r="E492">
-        <v>80.40000000000001</v>
+        <v>80.99481464884033</v>
       </c>
     </row>
     <row r="493" spans="1:5">
@@ -8761,13 +8761,13 @@
         <v>0</v>
       </c>
       <c r="C493">
-        <v>20.1</v>
+        <v>30.1</v>
       </c>
       <c r="D493">
         <v>201</v>
       </c>
       <c r="E493">
-        <v>60.3</v>
+        <v>64.29688950485864</v>
       </c>
     </row>
     <row r="494" spans="1:5">
@@ -8778,13 +8778,13 @@
         <v>0</v>
       </c>
       <c r="C494">
-        <v>40.3</v>
+        <v>20.1</v>
       </c>
       <c r="D494">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E494">
-        <v>80.60031017310044</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="495" spans="1:5">
@@ -8795,13 +8795,13 @@
         <v>0</v>
       </c>
       <c r="C495">
-        <v>50.2</v>
+        <v>30.1</v>
       </c>
       <c r="D495">
-        <v>301</v>
+        <v>201</v>
       </c>
       <c r="E495">
-        <v>102.8599047248246</v>
+        <v>64.29688950485864</v>
       </c>
     </row>
     <row r="496" spans="1:5">
@@ -8812,13 +8812,13 @@
         <v>0</v>
       </c>
       <c r="C496">
-        <v>910.8</v>
+        <v>30.2</v>
       </c>
       <c r="D496">
-        <v>8605</v>
+        <v>201</v>
       </c>
       <c r="E496">
-        <v>2565.959111131742</v>
+        <v>64.40621088062858</v>
       </c>
     </row>
     <row r="497" spans="1:5">
@@ -8829,13 +8829,13 @@
         <v>0</v>
       </c>
       <c r="C497">
-        <v>30.3</v>
+        <v>720.6</v>
       </c>
       <c r="D497">
-        <v>201</v>
+        <v>6804</v>
       </c>
       <c r="E497">
-        <v>64.516742013217</v>
+        <v>2029.349018774247</v>
       </c>
     </row>
     <row r="498" spans="1:5">
@@ -8846,13 +8846,13 @@
         <v>0</v>
       </c>
       <c r="C498">
-        <v>120.6</v>
+        <v>190.4</v>
       </c>
       <c r="D498">
-        <v>702</v>
+        <v>1502</v>
       </c>
       <c r="E498">
-        <v>218.9909587174776</v>
+        <v>444.3292022813716</v>
       </c>
     </row>
     <row r="499" spans="1:5">
@@ -8863,13 +8863,13 @@
         <v>0</v>
       </c>
       <c r="C499">
-        <v>30.3</v>
+        <v>220.2</v>
       </c>
       <c r="D499">
-        <v>202</v>
+        <v>1001</v>
       </c>
       <c r="E499">
-        <v>64.67155479807177</v>
+        <v>392.3164029198881</v>
       </c>
     </row>
     <row r="500" spans="1:5">
@@ -8880,13 +8880,13 @@
         <v>0</v>
       </c>
       <c r="C500">
-        <v>30.1</v>
+        <v>100.1</v>
       </c>
       <c r="D500">
-        <v>201</v>
+        <v>1001</v>
       </c>
       <c r="E500">
-        <v>64.29688950485863</v>
+        <v>300.3</v>
       </c>
     </row>
     <row r="501" spans="1:5">
@@ -8897,13 +8897,13 @@
         <v>0</v>
       </c>
       <c r="C501">
-        <v>59254039.2</v>
+        <v>71492165.40000001</v>
       </c>
       <c r="D501">
-        <v>122995671</v>
+        <v>184052514</v>
       </c>
       <c r="E501">
-        <v>44004725.64211901</v>
+        <v>55233135.05390218</v>
       </c>
     </row>
   </sheetData>
